--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45103</v>
+        <v>46183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>12.6</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1186,46 +1186,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45590</v>
+        <v>45331</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,17 +1255,17 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1295,42 +1295,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46183</v>
+        <v>45358</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1400,42 +1400,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45331</v>
+        <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,16 +1465,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45358</v>
+        <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45069</v>
+        <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45216</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45448</v>
+        <v>45370</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44641</v>
+        <v>45741</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45365</v>
+        <v>45812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45416</v>
+        <v>45901</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45883</v>
+        <v>45197</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44669</v>
+        <v>45275</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44642</v>
+        <v>45939</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>16.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2716,7 +2716,7 @@
         <v>45838</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2782,14 +2782,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45738</v>
+        <v>45916</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 44495-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44670</v>
+        <v>45916</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45901</v>
+        <v>45838</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45275</v>
+        <v>45416</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45838</v>
+        <v>44970</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44495-2025</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45916</v>
+        <v>45738</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45092</v>
+        <v>45190</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45099</v>
+        <v>45216</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>8.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45916</v>
+        <v>45448</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46083</v>
+        <v>45883</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45266</v>
+        <v>46083</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45957</v>
+        <v>45053</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45197</v>
+        <v>45184</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45520</v>
+        <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45772</v>
+        <v>45957</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45772</v>
+        <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45772</v>
+        <v>45673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45548</v>
+        <v>45525</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45092</v>
+        <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44970</v>
+        <v>44641</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45216</v>
+        <v>45772</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.1</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45433</v>
+        <v>45772</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45883</v>
+        <v>45772</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45741</v>
+        <v>45331</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44571</v>
+        <v>45197</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>11.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45520</v>
+        <v>44768</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45939</v>
+        <v>45365</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>16.1</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44983</v>
+        <v>45673</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4833,7 +4833,7 @@
         <v>45673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45673</v>
+        <v>45842</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4972,14 +4972,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45842</v>
+        <v>45709</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>6.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45190</v>
+        <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45197</v>
+        <v>46188</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>11.6</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5191,14 +5191,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45707</v>
+        <v>44917</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5210,8 +5210,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44768</v>
+        <v>44669</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46184</v>
+        <v>45309</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44518</v>
+        <v>45356</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46188</v>
+        <v>45936</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45216</v>
+        <v>44945</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45673</v>
+        <v>46195</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45673</v>
+        <v>46274</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5722,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5765,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45331</v>
+        <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44623</v>
+        <v>45548</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5868,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45356</v>
+        <v>44518</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44945</v>
+        <v>45520</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6071,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45053</v>
+        <v>44571</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6087,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6130,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44917</v>
+        <v>44642</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6159,13 +6164,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6218,14 +6218,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45709</v>
+        <v>45099</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.7</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45936</v>
+        <v>45216</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45258</v>
+        <v>45266</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45184</v>
+        <v>45092</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45219</v>
+        <v>45069</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6583,14 +6583,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46195</v>
+        <v>45707</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46274</v>
+        <v>45092</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45309</v>
+        <v>45258</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45525</v>
+        <v>44983</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45782</v>
+        <v>44670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45741</v>
+        <v>45520</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45296</v>
+        <v>45782</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45370</v>
+        <v>45741</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45812</v>
+        <v>45296</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7247,7 +7247,7 @@
         <v>45106</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45677</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45301</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45770</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45839</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45951</v>
+        <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,17 +1045,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1085,42 +1085,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 51772-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46183</v>
+        <v>45951</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>12.6</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1190,42 +1190,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45331</v>
+        <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1295,42 +1295,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45358</v>
+        <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>12.6</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1400,35 +1400,35 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 9520-2022</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44616</v>
+        <v>45069</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45433</v>
+        <v>44768</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 9520-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45370</v>
+        <v>45216</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45741</v>
+        <v>44518</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45812</v>
+        <v>45883</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45901</v>
+        <v>46083</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45197</v>
+        <v>45216</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45275</v>
+        <v>45901</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45939</v>
+        <v>44641</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>16.1</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45838</v>
+        <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.3</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45916</v>
+        <v>45365</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44495-2025</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45916</v>
+        <v>45838</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 44495-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45838</v>
+        <v>45916</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45416</v>
+        <v>45916</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44970</v>
+        <v>45416</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45738</v>
+        <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45190</v>
+        <v>45673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45216</v>
+        <v>44669</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.1</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45448</v>
+        <v>44642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3446,7 +3446,7 @@
         <v>45883</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3512,14 +3512,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46083</v>
+        <v>45738</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45053</v>
+        <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45184</v>
+        <v>45957</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45216</v>
+        <v>45275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45957</v>
+        <v>45092</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45673</v>
+        <v>45099</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45673</v>
+        <v>45266</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45525</v>
+        <v>45772</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45883</v>
+        <v>45772</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44641</v>
+        <v>45772</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45772</v>
+        <v>45331</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45772</v>
+        <v>45842</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45772</v>
+        <v>44623</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45331</v>
+        <v>45356</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4541,7 +4541,7 @@
         <v>45197</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>11.6</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44768</v>
+        <v>45741</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45365</v>
+        <v>45520</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45673</v>
+        <v>44945</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45673</v>
+        <v>45548</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45842</v>
+        <v>45939</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>16.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4972,14 +4972,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45709</v>
+        <v>45053</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.7</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46184</v>
+        <v>45092</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46188</v>
+        <v>44970</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44917</v>
+        <v>45216</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5210,13 +5210,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44669</v>
+        <v>45433</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5289,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45309</v>
+        <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45356</v>
+        <v>44571</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45936</v>
+        <v>45520</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44945</v>
+        <v>46188</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5581,7 +5576,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46195</v>
+        <v>44917</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5653,8 +5648,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46274</v>
+        <v>44983</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5780,14 +5780,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45219</v>
+        <v>45709</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45548</v>
+        <v>45673</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44518</v>
+        <v>45673</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45520</v>
+        <v>45190</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44571</v>
+        <v>45197</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>11.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44642</v>
+        <v>45258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45099</v>
+        <v>45184</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6291,14 +6291,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45216</v>
+        <v>45707</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45266</v>
+        <v>45936</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45092</v>
+        <v>45219</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45069</v>
+        <v>46195</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6583,14 +6583,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45707</v>
+        <v>45309</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45092</v>
+        <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45258</v>
+        <v>45525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>8.4</v>
+        <v>0.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44983</v>
+        <v>45782</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44670</v>
+        <v>45741</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45520</v>
+        <v>45296</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45782</v>
+        <v>45370</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45741</v>
+        <v>45812</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45296</v>
+        <v>45838</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7247,7 +7247,7 @@
         <v>45106</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45677</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45301</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45770</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45839</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 51772-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45331</v>
+        <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,16 +1045,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1085,42 +1085,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45951</v>
+        <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,17 +1150,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1190,35 +1190,35 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 9520-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45069</v>
+        <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44768</v>
+        <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 9520-2022</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44616</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45216</v>
+        <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44518</v>
+        <v>45197</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45883</v>
+        <v>45275</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46083</v>
+        <v>45812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45216</v>
+        <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45901</v>
+        <v>45416</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44641</v>
+        <v>44970</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45448</v>
+        <v>45738</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45365</v>
+        <v>45190</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45838</v>
+        <v>45216</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.3</v>
+        <v>8.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44495-2025</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45916</v>
+        <v>45448</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45916</v>
+        <v>45838</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45416</v>
+        <v>45838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45673</v>
+        <v>45916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 44495-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45673</v>
+        <v>45916</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44669</v>
+        <v>45053</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44642</v>
+        <v>45184</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45883</v>
+        <v>45939</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>16.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3512,14 +3512,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45738</v>
+        <v>45883</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44670</v>
+        <v>45216</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3665,7 +3665,7 @@
         <v>45957</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45275</v>
+        <v>45673</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45092</v>
+        <v>45673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45099</v>
+        <v>45525</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45266</v>
+        <v>44641</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45772</v>
+        <v>45331</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4103,7 +4103,7 @@
         <v>45772</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45772</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45331</v>
+        <v>45197</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>11.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45842</v>
+        <v>45772</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44623</v>
+        <v>44768</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45356</v>
+        <v>46083</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45197</v>
+        <v>45365</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45741</v>
+        <v>45673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45520</v>
+        <v>45673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4753,14 +4753,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44945</v>
+        <v>45709</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>6.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45548</v>
+        <v>44917</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4845,8 +4845,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45939</v>
+        <v>44669</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>16.1</v>
+        <v>3.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45053</v>
+        <v>45309</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45092</v>
+        <v>45883</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44970</v>
+        <v>45356</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45216</v>
+        <v>44945</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.1</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45433</v>
+        <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46184</v>
+        <v>45548</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44571</v>
+        <v>45842</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45520</v>
+        <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46188</v>
+        <v>45520</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44917</v>
+        <v>46184</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5648,13 +5653,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44983</v>
+        <v>46188</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5780,14 +5780,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45709</v>
+        <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45673</v>
+        <v>44642</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45673</v>
+        <v>45099</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45190</v>
+        <v>45216</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45197</v>
+        <v>45266</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>11.6</v>
+        <v>6.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45258</v>
+        <v>45092</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45184</v>
+        <v>45069</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6298,7 +6298,7 @@
         <v>45707</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45936</v>
+        <v>45092</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45219</v>
+        <v>45936</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>46195</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45309</v>
+        <v>45258</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46274</v>
+        <v>44983</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45525</v>
+        <v>44670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45782</v>
+        <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45741</v>
+        <v>45520</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45296</v>
+        <v>45782</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45370</v>
+        <v>45741</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45812</v>
+        <v>45296</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45838</v>
+        <v>45370</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7247,7 +7247,7 @@
         <v>45106</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45677</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45301</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45770</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45839</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45951</v>
+        <v>45103</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1081,46 +1081,46 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 51772-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45331</v>
+        <v>45951</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1190,42 +1190,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45358</v>
+        <v>46183</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>12.6</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1295,42 +1295,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46183</v>
+        <v>45590</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.6</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1400,42 +1400,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45103</v>
+        <v>45331</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45590</v>
+        <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45433</v>
+        <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>45216</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45741</v>
+        <v>44641</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45197</v>
+        <v>45448</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45275</v>
+        <v>45365</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45812</v>
+        <v>45416</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45901</v>
+        <v>45883</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45416</v>
+        <v>44669</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44970</v>
+        <v>44642</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45738</v>
+        <v>46083</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45190</v>
+        <v>45838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2855,14 +2855,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45216</v>
+        <v>45738</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45448</v>
+        <v>44670</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45838</v>
+        <v>45275</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.3</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45838</v>
+        <v>45092</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45916</v>
+        <v>45099</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44495-2025</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45916</v>
+        <v>45266</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45053</v>
+        <v>45901</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45184</v>
+        <v>45838</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.6</v>
+        <v>6.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 44495-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45939</v>
+        <v>45916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>16.1</v>
+        <v>5.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3519,7 +3519,7 @@
         <v>45883</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45216</v>
+        <v>45916</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45957</v>
+        <v>45197</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45673</v>
+        <v>45520</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45673</v>
+        <v>45548</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45525</v>
+        <v>45092</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.1</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44641</v>
+        <v>44970</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45331</v>
+        <v>45216</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45772</v>
+        <v>45433</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45772</v>
+        <v>45842</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45197</v>
+        <v>44571</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>11.6</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45772</v>
+        <v>45520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44768</v>
+        <v>44983</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46083</v>
+        <v>46184</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45365</v>
+        <v>45957</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45673</v>
+        <v>46188</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4687,7 +4687,7 @@
         <v>45673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4753,14 +4753,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45709</v>
+        <v>45673</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6.7</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44917</v>
+        <v>45190</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4845,13 +4845,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44669</v>
+        <v>45197</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.7</v>
+        <v>11.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4977,14 +4972,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45309</v>
+        <v>45707</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45883</v>
+        <v>44768</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5113,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5127,10 +5122,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45356</v>
+        <v>45772</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5143,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5186,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44945</v>
+        <v>45772</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5216,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45219</v>
+        <v>45772</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5332,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45548</v>
+        <v>44518</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45842</v>
+        <v>45936</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44518</v>
+        <v>45216</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45520</v>
+        <v>46195</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5624,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46184</v>
+        <v>45673</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5654,7 +5649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5711,10 +5706,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46188</v>
+        <v>45673</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44571</v>
+        <v>46274</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44642</v>
+        <v>45741</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45099</v>
+        <v>45331</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45216</v>
+        <v>44623</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45266</v>
+        <v>45356</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45092</v>
+        <v>44945</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45069</v>
+        <v>45053</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6233,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6291,14 +6286,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45707</v>
+        <v>45939</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6306,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.2</v>
+        <v>16.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6363,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45092</v>
+        <v>44917</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6383,8 +6378,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6437,14 +6437,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45936</v>
+        <v>45709</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>6.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46195</v>
+        <v>45258</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45258</v>
+        <v>45184</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44983</v>
+        <v>45219</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44670</v>
+        <v>45309</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46274</v>
+        <v>45525</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45520</v>
+        <v>45782</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45782</v>
+        <v>45741</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45741</v>
+        <v>45296</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45296</v>
+        <v>45370</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45370</v>
+        <v>45812</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7247,7 +7247,7 @@
         <v>45106</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45677</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45301</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45770</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45839</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 51772-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45103</v>
+        <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1081,46 +1081,46 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45951</v>
+        <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,17 +1150,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1190,42 +1190,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46183</v>
+        <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12.6</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1295,42 +1295,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45590</v>
+        <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>12.6</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1400,42 +1400,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45331</v>
+        <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,16 +1465,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45358</v>
+        <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45069</v>
+        <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45216</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44641</v>
+        <v>45197</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45448</v>
+        <v>45275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45365</v>
+        <v>45416</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45416</v>
+        <v>44970</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45883</v>
+        <v>45738</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44669</v>
+        <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44642</v>
+        <v>45216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>8.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46083</v>
+        <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45838</v>
+        <v>45053</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2855,14 +2855,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45738</v>
+        <v>45184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44670</v>
+        <v>45216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45275</v>
+        <v>45673</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45092</v>
+        <v>45673</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45099</v>
+        <v>45883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45266</v>
+        <v>45525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.2</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45901</v>
+        <v>44641</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45838</v>
+        <v>45331</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 44495-2025</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45916</v>
+        <v>45197</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.2</v>
+        <v>11.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45883</v>
+        <v>44768</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45916</v>
+        <v>45365</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45197</v>
+        <v>45901</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45520</v>
+        <v>45673</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45548</v>
+        <v>45673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45092</v>
+        <v>45838</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44970</v>
+        <v>45916</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 44495-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45216</v>
+        <v>45916</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.1</v>
+        <v>5.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45433</v>
+        <v>45709</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45842</v>
+        <v>44917</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4188,8 +4188,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4237,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4251,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44571</v>
+        <v>45957</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4267,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4324,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45520</v>
+        <v>44669</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4340,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44983</v>
+        <v>45309</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4456,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4470,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46184</v>
+        <v>45842</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4486,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4529,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4543,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45957</v>
+        <v>45356</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4597,7 +4602,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4616,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46188</v>
+        <v>44945</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4632,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4675,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4689,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45673</v>
+        <v>45772</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4705,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4748,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4762,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45673</v>
+        <v>45772</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4778,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45190</v>
+        <v>45772</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4851,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45197</v>
+        <v>45219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>11.6</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4972,14 +4977,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45707</v>
+        <v>45548</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44768</v>
+        <v>44518</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45772</v>
+        <v>45741</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45772</v>
+        <v>45520</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45772</v>
+        <v>45939</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44518</v>
+        <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45936</v>
+        <v>46083</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45216</v>
+        <v>46188</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46195</v>
+        <v>44571</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5619,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45673</v>
+        <v>44642</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45673</v>
+        <v>45099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5765,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46274</v>
+        <v>45216</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45741</v>
+        <v>45266</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5868,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45331</v>
+        <v>45092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44623</v>
+        <v>45069</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6067,14 +6072,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45356</v>
+        <v>45707</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6087,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6130,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44945</v>
+        <v>45092</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6160,7 +6165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6203,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6217,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45053</v>
+        <v>45258</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6233,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6276,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6290,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45939</v>
+        <v>44983</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6306,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>16.1</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6349,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6363,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44917</v>
+        <v>44670</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6378,13 +6383,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6437,14 +6437,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45709</v>
+        <v>45520</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45258</v>
+        <v>45936</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.4</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45184</v>
+        <v>45782</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45219</v>
+        <v>46195</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45309</v>
+        <v>45741</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45525</v>
+        <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45782</v>
+        <v>45296</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45741</v>
+        <v>45370</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45296</v>
+        <v>45812</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45370</v>
+        <v>45838</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45812</v>
+        <v>45883</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7247,7 +7247,7 @@
         <v>45106</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45677</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45301</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45770</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45839</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45197</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45416</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44970</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45738</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45053</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45673</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45673</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>44641</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45331</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45197</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>44768</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45365</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45901</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45673</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45838</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45916</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45916</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45709</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>44917</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45957</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44669</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45309</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45842</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>45356</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44945</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>45772</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45772</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45772</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45548</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>44518</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45741</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45520</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45939</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>46083</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>46188</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>44571</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>44642</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45216</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45266</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45069</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>45707</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45092</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>45258</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44983</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44670</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45520</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45936</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>45782</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>46195</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45741</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45296</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45370</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45812</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45838</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45883</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45106</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45677</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45301</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45770</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45839</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE92"/>
+  <dimension ref="A1:AE91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45331</v>
+        <v>46183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>12.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1190,42 +1190,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45358</v>
+        <v>45331</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,17 +1255,17 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1295,42 +1295,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46183</v>
+        <v>45358</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1400,35 +1400,35 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45197</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45416</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44970</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45738</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45053</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45673</v>
+        <v>45883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3081,7 +3081,7 @@
         <v>45673</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3154,7 +3154,7 @@
         <v>45883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45525</v>
+        <v>45673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44641</v>
+        <v>45901</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45331</v>
+        <v>45525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45197</v>
+        <v>45838</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>11.6</v>
+        <v>6.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44768</v>
+        <v>44641</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45365</v>
+        <v>45331</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45901</v>
+        <v>45197</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.9</v>
+        <v>11.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45673</v>
+        <v>44768</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45673</v>
+        <v>45365</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45838</v>
+        <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45916</v>
+        <v>45673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 44495-2025</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45916</v>
+        <v>45842</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45709</v>
+        <v>45957</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.7</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4169,14 +4169,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44917</v>
+        <v>45709</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4188,13 +4188,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>6.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4237,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4251,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45957</v>
+        <v>44917</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4266,8 +4261,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4310,7 +4310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44669</v>
+        <v>45772</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45309</v>
+        <v>45772</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45842</v>
+        <v>45772</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45356</v>
+        <v>44669</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44945</v>
+        <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45772</v>
+        <v>45356</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45772</v>
+        <v>45741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45772</v>
+        <v>44945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45219</v>
+        <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45548</v>
+        <v>46188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44518</v>
+        <v>45939</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>16.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45741</v>
+        <v>45219</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45520</v>
+        <v>45548</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45939</v>
+        <v>46083</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>16.1</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46184</v>
+        <v>44518</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46083</v>
+        <v>45520</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46188</v>
+        <v>44571</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44571</v>
+        <v>44642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44642</v>
+        <v>45099</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45099</v>
+        <v>46195</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5787,7 +5787,7 @@
         <v>45216</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45266</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45092</v>
+        <v>46274</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45069</v>
+        <v>45092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6072,14 +6072,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45707</v>
+        <v>45069</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6145,14 +6145,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45092</v>
+        <v>45707</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45258</v>
+        <v>45092</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44983</v>
+        <v>45916</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44670</v>
+        <v>45936</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45520</v>
+        <v>45258</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45936</v>
+        <v>44983</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45782</v>
+        <v>44670</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46195</v>
+        <v>45520</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45741</v>
+        <v>45782</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46274</v>
+        <v>45741</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>45296</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45370</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45812</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45838</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7157,24 +7157,24 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>S 2341-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45883</v>
+        <v>45106</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S 2341-2023</t>
+          <t>S 173-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45106</v>
+        <v>45677</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>25.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S 173-2025</t>
+          <t>S 92-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45677</v>
+        <v>45301</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>25.3</v>
+        <v>11.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S 92-2024</t>
+          <t>S 1331-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45301</v>
+        <v>45770</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>11.9</v>
+        <v>3.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7446,10 +7446,10 @@
       </c>
       <c r="V90" s="2" t="inlineStr"/>
     </row>
-    <row r="91" ht="15" customHeight="1">
+    <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S 1331-2025</t>
+          <t>S 2061-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7459,14 +7459,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45770</v>
+        <v>45839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7518,79 +7518,6 @@
         <v>0</v>
       </c>
       <c r="V91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>S 2061-2025</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="E92" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45951</v>
+        <v>45103</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1081,46 +1081,46 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46183</v>
+        <v>45590</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>12.6</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1190,42 +1190,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 51772-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45331</v>
+        <v>45951</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1295,42 +1295,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45358</v>
+        <v>45331</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1360,17 +1360,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1400,42 +1400,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45103</v>
+        <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45590</v>
+        <v>46183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>12.6</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45433</v>
+        <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>45197</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45197</v>
+        <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45275</v>
+        <v>45883</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45416</v>
+        <v>45548</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44970</v>
+        <v>45370</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45738</v>
+        <v>45216</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45190</v>
+        <v>45092</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45216</v>
+        <v>44970</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45448</v>
+        <v>45216</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>8.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45053</v>
+        <v>45433</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45184</v>
+        <v>45901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45216</v>
+        <v>44571</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45883</v>
+        <v>45520</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45673</v>
+        <v>45838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>6.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45883</v>
+        <v>44641</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45673</v>
+        <v>45448</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45901</v>
+        <v>44983</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45525</v>
+        <v>45365</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45838</v>
+        <v>45812</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44641</v>
+        <v>45416</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45331</v>
+        <v>45673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45197</v>
+        <v>45673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>11.6</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44768</v>
+        <v>44669</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45365</v>
+        <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45673</v>
+        <v>45190</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45673</v>
+        <v>45197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>11.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45842</v>
+        <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45957</v>
+        <v>45738</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4169,14 +4169,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45709</v>
+        <v>44670</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44917</v>
+        <v>45275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4261,13 +4261,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4310,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4324,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45772</v>
+        <v>45092</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4340,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4383,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4393,14 +4388,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45772</v>
+        <v>45707</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4413,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4456,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4470,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45772</v>
+        <v>45099</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4486,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4529,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4543,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44669</v>
+        <v>44768</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4559,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4602,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4616,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45309</v>
+        <v>45772</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4632,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4675,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4689,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45356</v>
+        <v>45772</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4705,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4748,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4762,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45741</v>
+        <v>45772</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4778,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4821,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44945</v>
+        <v>45266</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4851,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46184</v>
+        <v>45741</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46188</v>
+        <v>45838</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45939</v>
+        <v>44518</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>16.1</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5113,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5127,10 +5122,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45219</v>
+        <v>45939</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5143,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5186,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45548</v>
+        <v>45216</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5216,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46083</v>
+        <v>45673</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5289,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44518</v>
+        <v>45673</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45520</v>
+        <v>45916</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44571</v>
+        <v>45936</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44642</v>
+        <v>46083</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5581,7 +5576,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45099</v>
+        <v>45331</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5654,7 +5649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5711,10 +5706,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46195</v>
+        <v>44623</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45216</v>
+        <v>45356</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45266</v>
+        <v>44945</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46274</v>
+        <v>45053</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45092</v>
+        <v>44917</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6018,8 +6013,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6072,14 +6072,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45069</v>
+        <v>45709</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6145,14 +6145,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45707</v>
+        <v>45883</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45092</v>
+        <v>45258</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45916</v>
+        <v>45184</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45936</v>
+        <v>45219</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45258</v>
+        <v>45309</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44983</v>
+        <v>45525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.8</v>
+        <v>0.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44670</v>
+        <v>45782</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45520</v>
+        <v>45741</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45782</v>
+        <v>45296</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45741</v>
+        <v>45842</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45296</v>
+        <v>46184</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45370</v>
+        <v>46188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45812</v>
+        <v>46195</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45838</v>
+        <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7174,7 +7174,7 @@
         <v>45106</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45677</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45301</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45770</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 51772-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45103</v>
+        <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1081,46 +1081,46 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45590</v>
+        <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,17 +1150,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1190,42 +1190,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45951</v>
+        <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1295,42 +1295,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45331</v>
+        <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1360,16 +1360,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>12.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1400,42 +1400,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45358</v>
+        <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46183</v>
+        <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>12.6</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45069</v>
+        <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45197</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45520</v>
+        <v>45197</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45883</v>
+        <v>45275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45548</v>
+        <v>45416</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2417,14 +2417,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45370</v>
+        <v>45738</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45216</v>
+        <v>44970</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45092</v>
+        <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44970</v>
+        <v>45216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>8.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45216</v>
+        <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45433</v>
+        <v>45053</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45901</v>
+        <v>45184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44571</v>
+        <v>45216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45520</v>
+        <v>45883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45838</v>
+        <v>45673</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44641</v>
+        <v>45901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45448</v>
+        <v>45673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44983</v>
+        <v>45883</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45365</v>
+        <v>45525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45812</v>
+        <v>44641</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45416</v>
+        <v>45838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45673</v>
+        <v>45331</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45673</v>
+        <v>45197</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>11.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44669</v>
+        <v>44768</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44642</v>
+        <v>45365</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45190</v>
+        <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45197</v>
+        <v>45673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>11.6</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4030,7 +4030,7 @@
         <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45738</v>
+        <v>45709</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44670</v>
+        <v>44917</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4188,8 +4188,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4237,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4251,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45275</v>
+        <v>45772</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4267,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4324,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45092</v>
+        <v>45772</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4340,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4388,14 +4393,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45707</v>
+        <v>44669</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4456,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4470,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45099</v>
+        <v>45772</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4486,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4529,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4543,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44768</v>
+        <v>45842</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4559,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4602,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4616,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45772</v>
+        <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4632,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4675,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4689,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45772</v>
+        <v>45356</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4705,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4748,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4762,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45772</v>
+        <v>44945</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4778,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45266</v>
+        <v>45741</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4851,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.2</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45741</v>
+        <v>45219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45838</v>
+        <v>45939</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>16.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44518</v>
+        <v>45548</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45939</v>
+        <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>16.1</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45216</v>
+        <v>45520</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45673</v>
+        <v>46083</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45673</v>
+        <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45916</v>
+        <v>46188</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45936</v>
+        <v>44571</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46083</v>
+        <v>44642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45331</v>
+        <v>45099</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44623</v>
+        <v>45216</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5722,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5765,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45356</v>
+        <v>45266</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>6.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44945</v>
+        <v>45092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5868,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45053</v>
+        <v>45069</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5994,14 +5999,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44917</v>
+        <v>45707</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6013,13 +6018,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6072,14 +6072,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45709</v>
+        <v>45092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45883</v>
+        <v>46195</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45258</v>
+        <v>46274</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45184</v>
+        <v>45258</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45219</v>
+        <v>44983</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45309</v>
+        <v>44670</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45525</v>
+        <v>45520</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6590,7 +6590,7 @@
         <v>45782</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45741</v>
+        <v>45916</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45296</v>
+        <v>45741</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45842</v>
+        <v>45296</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46184</v>
+        <v>45370</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46188</v>
+        <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46195</v>
+        <v>45812</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46274</v>
+        <v>45838</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7174,7 +7174,7 @@
         <v>45106</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45677</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45301</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45770</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45331</v>
+        <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1186,46 +1186,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45358</v>
+        <v>46183</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>12.6</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1295,42 +1295,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46183</v>
+        <v>45590</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.6</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1400,42 +1400,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45103</v>
+        <v>45331</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45590</v>
+        <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45433</v>
+        <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>45216</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45197</v>
+        <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45275</v>
+        <v>45370</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45416</v>
+        <v>45883</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2417,14 +2417,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45738</v>
+        <v>44641</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44970</v>
+        <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45190</v>
+        <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>16.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45216</v>
+        <v>45448</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45448</v>
+        <v>45365</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45053</v>
+        <v>45838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>6.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45184</v>
+        <v>45416</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45216</v>
+        <v>46083</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45883</v>
+        <v>44669</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45673</v>
+        <v>44642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45901</v>
+        <v>45738</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45673</v>
+        <v>44670</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45883</v>
+        <v>45275</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45525</v>
+        <v>45957</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44641</v>
+        <v>45092</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45838</v>
+        <v>45812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45331</v>
+        <v>45099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45197</v>
+        <v>45266</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>11.6</v>
+        <v>6.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44768</v>
+        <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45365</v>
+        <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45673</v>
+        <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45673</v>
+        <v>45883</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45957</v>
+        <v>45197</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45709</v>
+        <v>45520</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44917</v>
+        <v>45548</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4188,13 +4188,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4237,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4251,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45772</v>
+        <v>45092</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4267,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4310,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4324,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45772</v>
+        <v>44970</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4340,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4383,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44669</v>
+        <v>45842</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4413,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4456,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4470,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45772</v>
+        <v>45838</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4486,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4529,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4543,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45842</v>
+        <v>45216</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4559,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.7</v>
+        <v>8.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4602,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4616,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45309</v>
+        <v>45433</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4632,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4675,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4689,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45356</v>
+        <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4705,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4748,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4762,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44945</v>
+        <v>45520</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4778,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4821,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45741</v>
+        <v>44983</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4851,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45219</v>
+        <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45939</v>
+        <v>46188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>16.1</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45548</v>
+        <v>45673</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5113,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5127,10 +5122,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44518</v>
+        <v>45673</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5143,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5186,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45520</v>
+        <v>45190</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5216,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46083</v>
+        <v>45197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5289,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>11.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5342,14 +5337,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46184</v>
+        <v>45707</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46188</v>
+        <v>44768</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44571</v>
+        <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44642</v>
+        <v>46195</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5581,7 +5576,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45099</v>
+        <v>46274</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5654,7 +5649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5714,7 +5709,7 @@
         <v>45216</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5770,7 +5765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45266</v>
+        <v>45673</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45092</v>
+        <v>45673</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45069</v>
+        <v>45916</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5999,14 +5994,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45707</v>
+        <v>45936</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45092</v>
+        <v>45331</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46195</v>
+        <v>44623</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46274</v>
+        <v>45356</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6233,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6290,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45258</v>
+        <v>44945</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6306,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6363,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44983</v>
+        <v>45053</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6379,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6422,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6436,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44670</v>
+        <v>44917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6456,8 +6451,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6510,14 +6510,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45520</v>
+        <v>45709</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>6.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45782</v>
+        <v>45258</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45916</v>
+        <v>45184</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45741</v>
+        <v>45219</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45296</v>
+        <v>45309</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45370</v>
+        <v>45525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45936</v>
+        <v>45782</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45812</v>
+        <v>45741</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45838</v>
+        <v>45296</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7174,7 +7174,7 @@
         <v>45106</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45677</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45301</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45770</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>46183</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45590</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45331</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45216</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45370</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45883</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44641</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45448</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45365</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45416</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>46083</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44669</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>44642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45738</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44670</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45275</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45957</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45092</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45266</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45883</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45197</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45520</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45548</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>45092</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44970</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45842</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45838</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45216</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>45433</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45520</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44983</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>46188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>45673</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45673</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45190</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45707</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44768</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>46195</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>46274</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45216</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45673</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45673</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>45916</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45936</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>45331</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44623</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>45356</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44945</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45053</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45709</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>45258</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45184</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45219</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>45309</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45782</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45741</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45296</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45106</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45677</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45301</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45770</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>46183</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45590</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45331</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45216</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45370</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45883</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44641</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45448</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45365</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45416</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>46083</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44669</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>44642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45738</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44670</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45275</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45957</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45092</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45266</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45883</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45197</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45520</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45548</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>45092</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44970</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45842</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45838</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45216</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>45433</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45520</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44983</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>46188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>45673</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45673</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45190</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45707</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44768</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>46195</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>46274</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45216</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45673</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45673</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>45916</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45936</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>45331</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44623</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>45356</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44945</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45053</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45709</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>45258</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45184</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45219</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>45309</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45782</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45741</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45296</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45106</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45677</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45301</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45770</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45103</v>
+        <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,17 +1150,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1186,46 +1186,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46183</v>
+        <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12.6</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1295,42 +1295,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45590</v>
+        <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>12.6</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1400,42 +1400,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45331</v>
+        <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,16 +1465,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45358</v>
+        <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45069</v>
+        <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45216</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45741</v>
+        <v>45370</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45370</v>
+        <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45883</v>
+        <v>45812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44641</v>
+        <v>45197</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45901</v>
+        <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45939</v>
+        <v>45275</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>16.1</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45448</v>
+        <v>45416</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45365</v>
+        <v>44970</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2789,7 +2789,7 @@
         <v>45838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2855,14 +2855,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45416</v>
+        <v>45738</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46083</v>
+        <v>45190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44669</v>
+        <v>45216</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>8.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44642</v>
+        <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45738</v>
+        <v>45741</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44670</v>
+        <v>45957</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45275</v>
+        <v>45053</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45957</v>
+        <v>45184</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45092</v>
+        <v>45883</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45812</v>
+        <v>45216</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45099</v>
+        <v>45939</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>16.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45266</v>
+        <v>45772</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3738,7 +3738,7 @@
         <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3811,7 +3811,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45772</v>
+        <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45883</v>
+        <v>45673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45197</v>
+        <v>45525</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45520</v>
+        <v>44641</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45548</v>
+        <v>45331</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45092</v>
+        <v>45197</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>11.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44970</v>
+        <v>44768</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45842</v>
+        <v>45365</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45838</v>
+        <v>46083</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45216</v>
+        <v>45673</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45433</v>
+        <v>45673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4680,14 +4680,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44571</v>
+        <v>45709</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45520</v>
+        <v>44917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4772,8 +4772,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44983</v>
+        <v>44669</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4851,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46184</v>
+        <v>45309</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46188</v>
+        <v>45883</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45673</v>
+        <v>45356</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45673</v>
+        <v>44945</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45190</v>
+        <v>45219</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45197</v>
+        <v>45842</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>11.6</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5337,14 +5342,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45707</v>
+        <v>45548</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44768</v>
+        <v>44518</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44518</v>
+        <v>45520</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46195</v>
+        <v>46184</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46274</v>
+        <v>46188</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45216</v>
+        <v>44571</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5722,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5765,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45673</v>
+        <v>44642</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45673</v>
+        <v>45099</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5911,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45916</v>
+        <v>45216</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45936</v>
+        <v>45266</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6071,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45331</v>
+        <v>45092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6087,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6130,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44623</v>
+        <v>45069</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6160,7 +6165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6203,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6213,14 +6218,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45356</v>
+        <v>45707</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6233,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6276,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6290,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44945</v>
+        <v>45092</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6306,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6349,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6363,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45053</v>
+        <v>46195</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6379,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6422,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6436,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44917</v>
+        <v>46274</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6451,13 +6456,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6510,14 +6510,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45709</v>
+        <v>45258</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45258</v>
+        <v>44983</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45184</v>
+        <v>44670</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45219</v>
+        <v>45520</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45309</v>
+        <v>45782</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45525</v>
+        <v>45741</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45782</v>
+        <v>45296</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45741</v>
+        <v>45916</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45296</v>
+        <v>45936</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7174,7 +7174,7 @@
         <v>45106</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45677</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45301</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45770</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE91"/>
+  <dimension ref="A1:AE92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45331</v>
+        <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1186,46 +1186,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45358</v>
+        <v>45590</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1295,35 +1295,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45103</v>
+        <v>45331</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45590</v>
+        <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45433</v>
+        <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>45216</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45370</v>
+        <v>45883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45901</v>
+        <v>45370</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45812</v>
+        <v>45741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45197</v>
+        <v>45901</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45838</v>
+        <v>44641</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45275</v>
+        <v>45448</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45416</v>
+        <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44970</v>
+        <v>45365</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45838</v>
+        <v>45416</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2855,14 +2855,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45738</v>
+        <v>45838</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45190</v>
+        <v>45838</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45216</v>
+        <v>44669</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.1</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45448</v>
+        <v>44642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45741</v>
+        <v>45738</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45957</v>
+        <v>45939</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>16.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45053</v>
+        <v>44670</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45184</v>
+        <v>45275</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45883</v>
+        <v>45957</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45216</v>
+        <v>45092</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45939</v>
+        <v>45099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>16.1</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45772</v>
+        <v>45266</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3738,7 +3738,7 @@
         <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3811,7 +3811,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45673</v>
+        <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45673</v>
+        <v>46083</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45525</v>
+        <v>45197</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44641</v>
+        <v>45520</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45331</v>
+        <v>45548</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45197</v>
+        <v>45092</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>11.6</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44768</v>
+        <v>44970</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45365</v>
+        <v>45216</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46083</v>
+        <v>45433</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45673</v>
+        <v>45883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45673</v>
+        <v>44571</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4680,14 +4680,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45709</v>
+        <v>45520</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44917</v>
+        <v>44983</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4772,13 +4772,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4821,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44669</v>
+        <v>45673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4851,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45309</v>
+        <v>45673</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45883</v>
+        <v>45190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45356</v>
+        <v>45197</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>11.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5113,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5127,10 +5122,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44945</v>
+        <v>45842</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5143,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5186,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5196,14 +5191,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45219</v>
+        <v>45707</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5216,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45842</v>
+        <v>44768</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5289,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45548</v>
+        <v>44518</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44518</v>
+        <v>46184</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45520</v>
+        <v>46188</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46184</v>
+        <v>45216</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5581,7 +5576,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46188</v>
+        <v>45673</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5654,7 +5649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5711,10 +5706,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44571</v>
+        <v>45673</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44642</v>
+        <v>45331</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45099</v>
+        <v>44623</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45216</v>
+        <v>45356</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45266</v>
+        <v>44945</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45092</v>
+        <v>45053</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45069</v>
+        <v>44917</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6164,8 +6159,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>6.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45092</v>
+        <v>46195</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46195</v>
+        <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46274</v>
+        <v>45258</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>8.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45258</v>
+        <v>45184</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44983</v>
+        <v>45219</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44670</v>
+        <v>45916</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45520</v>
+        <v>45309</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45782</v>
+        <v>45936</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45741</v>
+        <v>45525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45296</v>
+        <v>45782</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45916</v>
+        <v>45741</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45936</v>
+        <v>45296</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,24 +7157,24 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S 2341-2023</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45106</v>
+        <v>46294</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S 173-2025</t>
+          <t>S 2341-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45677</v>
+        <v>45106</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>25.3</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S 92-2024</t>
+          <t>S 173-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45301</v>
+        <v>45677</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>11.9</v>
+        <v>25.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,148 +7376,221 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
+          <t>S 92-2024</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>S 1331-2025</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D90" s="1" t="n">
+      <c r="D91" s="1" t="n">
         <v>45770</v>
       </c>
-      <c r="E90" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
+      <c r="E91" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
         <v>3.5</v>
       </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>S 2061-2025</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D91" s="1" t="n">
+      <c r="D92" s="1" t="n">
         <v>45839</v>
       </c>
-      <c r="E91" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
+      <c r="E92" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="2" t="inlineStr"/>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE92"/>
+  <dimension ref="A1:AE93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45951</v>
+        <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,17 +1045,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1085,42 +1085,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45103</v>
+        <v>45358</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1186,39 +1186,39 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>45590</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46183</v>
+        <v>45103</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.6</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1396,252 +1396,252 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 51772-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 26455-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>Myskmadra</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 5339-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45331</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Kösa</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 9316-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45358</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45069</v>
+        <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45216</v>
+        <v>45053</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45883</v>
+        <v>45092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45370</v>
+        <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45741</v>
+        <v>45184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2417,14 +2417,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45901</v>
+        <v>45707</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44641</v>
+        <v>45219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45448</v>
+        <v>45092</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45812</v>
+        <v>45216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45365</v>
+        <v>45548</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45416</v>
+        <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45838</v>
+        <v>45520</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45838</v>
+        <v>45673</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44669</v>
+        <v>45673</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44642</v>
+        <v>45525</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45738</v>
+        <v>44641</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45939</v>
+        <v>45258</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>16.1</v>
+        <v>8.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44670</v>
+        <v>44983</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45275</v>
+        <v>44670</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45957</v>
+        <v>45331</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45092</v>
+        <v>45520</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45099</v>
+        <v>45197</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45266</v>
+        <v>44623</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45772</v>
+        <v>44768</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45772</v>
+        <v>45365</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45772</v>
+        <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46083</v>
+        <v>45673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45197</v>
+        <v>45782</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45520</v>
+        <v>45741</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45548</v>
+        <v>45296</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45092</v>
+        <v>45370</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44970</v>
+        <v>44571</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4388,14 +4388,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45216</v>
+        <v>45709</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45433</v>
+        <v>45197</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45883</v>
+        <v>44642</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44571</v>
+        <v>44917</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4626,8 +4626,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4675,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4689,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45520</v>
+        <v>45812</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4705,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4748,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4762,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44983</v>
+        <v>45275</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4778,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45673</v>
+        <v>44669</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4851,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45673</v>
+        <v>45099</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45190</v>
+        <v>45309</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45197</v>
+        <v>45416</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>11.6</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45842</v>
+        <v>44970</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5191,14 +5196,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45707</v>
+        <v>45356</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44768</v>
+        <v>45216</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44518</v>
+        <v>45838</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46184</v>
+        <v>45266</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5483,14 +5488,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46188</v>
+        <v>45738</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45216</v>
+        <v>45190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45673</v>
+        <v>44945</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45673</v>
+        <v>45216</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5722,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>8.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5765,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45331</v>
+        <v>45448</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44623</v>
+        <v>45883</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5868,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45356</v>
+        <v>45901</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44945</v>
+        <v>45957</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6071,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45053</v>
+        <v>45838</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6087,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>6.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6130,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44917</v>
+        <v>45772</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6159,13 +6164,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6218,14 +6218,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45709</v>
+        <v>45772</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46195</v>
+        <v>45772</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46274</v>
+        <v>45741</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45258</v>
+        <v>45939</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.4</v>
+        <v>16.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45184</v>
+        <v>46083</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45219</v>
+        <v>45883</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45916</v>
+        <v>45842</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45309</v>
+        <v>46184</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45936</v>
+        <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45525</v>
+        <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45782</v>
+        <v>45916</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45741</v>
+        <v>45936</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45296</v>
+        <v>46295</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7174,7 +7174,7 @@
         <v>46294</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7230,24 +7230,24 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S 2341-2023</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45106</v>
+        <v>46195</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S 173-2025</t>
+          <t>S 2341-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45677</v>
+        <v>45106</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>25.3</v>
+        <v>21</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S 92-2024</t>
+          <t>S 173-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45301</v>
+        <v>45677</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>11.9</v>
+        <v>25.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,148 +7449,221 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
+          <t>S 92-2024</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>S 1331-2025</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D91" s="1" t="n">
+      <c r="D92" s="1" t="n">
         <v>45770</v>
       </c>
-      <c r="E91" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
+      <c r="E92" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
         <v>3.5</v>
       </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>S 2061-2025</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D92" s="1" t="n">
+      <c r="D93" s="1" t="n">
         <v>45839</v>
       </c>
-      <c r="E92" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
+      <c r="E93" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" s="2" t="inlineStr"/>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 51772-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45331</v>
+        <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,16 +1045,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1085,42 +1085,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45358</v>
+        <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1186,39 +1186,39 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>45590</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45103</v>
+        <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>12.6</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1396,46 +1396,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45951</v>
+        <v>45331</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1505,42 +1505,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46183</v>
+        <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>12.6</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45433</v>
+        <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45053</v>
+        <v>45216</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45092</v>
+        <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45069</v>
+        <v>45883</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45184</v>
+        <v>45370</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2417,14 +2417,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45707</v>
+        <v>45939</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>16.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45219</v>
+        <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45092</v>
+        <v>44641</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45216</v>
+        <v>45448</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45548</v>
+        <v>45838</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44518</v>
+        <v>45365</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45520</v>
+        <v>45416</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45673</v>
+        <v>46083</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45673</v>
+        <v>44669</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45525</v>
+        <v>44642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.1</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44641</v>
+        <v>45957</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45258</v>
+        <v>45812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44983</v>
+        <v>45738</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         <v>44670</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45331</v>
+        <v>45275</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45520</v>
+        <v>45092</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45197</v>
+        <v>45099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44623</v>
+        <v>45772</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44768</v>
+        <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45365</v>
+        <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45673</v>
+        <v>45883</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45673</v>
+        <v>45266</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45782</v>
+        <v>45838</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45741</v>
+        <v>45197</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45296</v>
+        <v>45520</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45370</v>
+        <v>45548</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44571</v>
+        <v>45092</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4388,14 +4388,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45709</v>
+        <v>44970</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45197</v>
+        <v>45216</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>8.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44642</v>
+        <v>45433</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44917</v>
+        <v>45842</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4626,13 +4626,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4675,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4689,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45812</v>
+        <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4705,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4748,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4762,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45275</v>
+        <v>45520</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4778,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4821,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44669</v>
+        <v>44983</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4851,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45099</v>
+        <v>45673</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45309</v>
+        <v>45673</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45416</v>
+        <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5113,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5127,10 +5122,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44970</v>
+        <v>45190</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5143,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5186,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45356</v>
+        <v>45197</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5216,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>11.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45216</v>
+        <v>46188</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5289,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5342,14 +5337,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45838</v>
+        <v>45707</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45266</v>
+        <v>44768</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5488,14 +5483,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45738</v>
+        <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45190</v>
+        <v>45216</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5581,7 +5576,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44945</v>
+        <v>45673</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5654,7 +5649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5711,10 +5706,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45216</v>
+        <v>45673</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8.1</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45448</v>
+        <v>46274</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45883</v>
+        <v>45331</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45901</v>
+        <v>44623</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45957</v>
+        <v>45356</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6062,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45838</v>
+        <v>44945</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45772</v>
+        <v>45916</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45772</v>
+        <v>45053</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6233,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6290,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45772</v>
+        <v>45936</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6306,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6363,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45741</v>
+        <v>44917</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6383,8 +6378,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45939</v>
+        <v>46294</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>16.1</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6510,14 +6510,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46083</v>
+        <v>45709</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45883</v>
+        <v>46195</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45842</v>
+        <v>45258</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>8.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46184</v>
+        <v>45184</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46188</v>
+        <v>46295</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46274</v>
+        <v>45219</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45916</v>
+        <v>45309</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45936</v>
+        <v>45525</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46295</v>
+        <v>45782</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46294</v>
+        <v>45741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46195</v>
+        <v>45296</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7320,7 +7320,7 @@
         <v>45106</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45677</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45770</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45839</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45103</v>
+        <v>46183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>12.6</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1186,462 +1186,462 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 5339-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45331</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Kösa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 9316-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45358</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 28478-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45103</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Dvärgpipistrell</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 48309-2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45590</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>1.5</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 26455-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 5339-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45331</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Kösa</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 9316-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45358</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45069</v>
+        <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45216</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2205,7 +2205,7 @@
         <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45883</v>
+        <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45370</v>
+        <v>45197</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45939</v>
+        <v>45370</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>16.1</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45901</v>
+        <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44641</v>
+        <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>16.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45448</v>
+        <v>45275</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45838</v>
+        <v>45416</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45365</v>
+        <v>44970</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2855,14 +2855,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45416</v>
+        <v>45738</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46083</v>
+        <v>45190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44669</v>
+        <v>45216</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>8.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44642</v>
+        <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45957</v>
+        <v>46083</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>45812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45738</v>
+        <v>45957</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44670</v>
+        <v>45053</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45275</v>
+        <v>45184</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45092</v>
+        <v>45216</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45099</v>
+        <v>45673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45772</v>
+        <v>45673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45883</v>
+        <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45266</v>
+        <v>45525</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.2</v>
+        <v>0.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45838</v>
+        <v>44641</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45197</v>
+        <v>45331</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45520</v>
+        <v>45197</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>11.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45548</v>
+        <v>44768</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45092</v>
+        <v>45365</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44970</v>
+        <v>45838</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45216</v>
+        <v>45673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45433</v>
+        <v>45673</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45842</v>
+        <v>45883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4680,14 +4680,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44571</v>
+        <v>45709</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45520</v>
+        <v>44917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4772,8 +4772,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44983</v>
+        <v>44669</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4851,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45673</v>
+        <v>45842</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45673</v>
+        <v>45309</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46184</v>
+        <v>45356</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45190</v>
+        <v>44945</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45197</v>
+        <v>45883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>11.6</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46188</v>
+        <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5337,14 +5342,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45707</v>
+        <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44768</v>
+        <v>46188</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44518</v>
+        <v>45548</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45216</v>
+        <v>44518</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45673</v>
+        <v>45520</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45673</v>
+        <v>46274</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5722,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5765,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46274</v>
+        <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45331</v>
+        <v>45916</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5868,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44623</v>
+        <v>45936</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45356</v>
+        <v>44642</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6071,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44945</v>
+        <v>45099</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6087,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6130,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45916</v>
+        <v>46295</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6160,7 +6165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6203,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6217,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45053</v>
+        <v>46294</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6233,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6276,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6290,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45936</v>
+        <v>46195</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6306,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6349,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6363,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44917</v>
+        <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6378,13 +6383,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46294</v>
+        <v>45266</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6510,14 +6510,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45709</v>
+        <v>45092</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46195</v>
+        <v>45069</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6656,14 +6656,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45258</v>
+        <v>45707</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>8.4</v>
+        <v>0.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45184</v>
+        <v>45092</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46295</v>
+        <v>45258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45219</v>
+        <v>44983</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45309</v>
+        <v>44670</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45525</v>
+        <v>45520</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7101,7 +7101,7 @@
         <v>45782</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45296</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45106</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45677</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45770</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45839</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>46183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45331</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45358</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45197</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45370</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45275</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45416</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44970</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45738</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45216</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>46083</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45957</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45053</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45184</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45216</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45525</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44641</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45331</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45197</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>44768</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45365</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45838</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45673</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>45883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>45709</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44669</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45842</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45309</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45356</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44945</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>46188</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45548</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>44518</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45520</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>46274</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45916</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45936</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44642</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>45099</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>46295</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>46294</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>46195</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45266</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45092</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>45069</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45707</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45092</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>45258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44983</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44670</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45520</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45782</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45296</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45106</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45677</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45770</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45839</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>46183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45331</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45358</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45197</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45370</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45275</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45416</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44970</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45738</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45216</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>46083</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45957</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45053</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45184</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45216</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45525</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44641</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45331</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45197</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>44768</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45365</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45838</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45673</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>45883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>45709</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44669</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45842</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45309</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45356</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44945</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>46188</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45548</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>44518</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45520</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>46274</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45916</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45936</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44642</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>45099</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>46295</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>46294</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>46195</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45266</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45092</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>45069</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45707</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45092</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>45258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44983</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44670</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45520</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45782</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45296</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45106</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45677</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45770</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45839</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE93"/>
+  <dimension ref="A1:AE94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46183</v>
+        <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>12.6</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1186,462 +1186,462 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 48309-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45590</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 26455-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Myskmadra</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 5339-2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45331</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>1.9</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Kösa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 9316-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45358</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Gröngöling</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 28478-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45103</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 48309-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45590</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45433</v>
+        <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>45216</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45741</v>
+        <v>44641</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45901</v>
+        <v>45448</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45197</v>
+        <v>45365</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45370</v>
+        <v>45883</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45838</v>
+        <v>45812</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2570,7 +2570,7 @@
         <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45275</v>
+        <v>45416</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45416</v>
+        <v>45838</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44970</v>
+        <v>45901</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2855,14 +2855,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45738</v>
+        <v>44669</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45190</v>
+        <v>44642</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45216</v>
+        <v>45838</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45448</v>
+        <v>45738</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46083</v>
+        <v>44670</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45812</v>
+        <v>45275</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45957</v>
+        <v>45092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45053</v>
+        <v>45099</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45184</v>
+        <v>45266</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45216</v>
+        <v>45957</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45673</v>
+        <v>46083</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45673</v>
+        <v>45197</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3738,7 +3738,7 @@
         <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3811,7 +3811,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3884,7 +3884,7 @@
         <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45525</v>
+        <v>45520</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44641</v>
+        <v>45548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45331</v>
+        <v>45092</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45197</v>
+        <v>44970</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>11.6</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44768</v>
+        <v>45216</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45365</v>
+        <v>45433</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45838</v>
+        <v>45883</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45673</v>
+        <v>45741</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45673</v>
+        <v>44571</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45883</v>
+        <v>45520</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4680,14 +4680,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45709</v>
+        <v>44983</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.7</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44917</v>
+        <v>45842</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4772,13 +4772,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4821,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44669</v>
+        <v>45673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4851,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45842</v>
+        <v>45673</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45309</v>
+        <v>45190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45356</v>
+        <v>45197</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>11.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5113,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5123,14 +5118,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44945</v>
+        <v>45707</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5143,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5186,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45883</v>
+        <v>44768</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5216,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45219</v>
+        <v>46184</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5289,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46188</v>
+        <v>44518</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45548</v>
+        <v>45216</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44518</v>
+        <v>45673</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5581,7 +5576,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45520</v>
+        <v>45673</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5654,7 +5649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5711,10 +5706,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46274</v>
+        <v>45331</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44571</v>
+        <v>44623</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45916</v>
+        <v>45356</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45936</v>
+        <v>44945</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44642</v>
+        <v>45053</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45099</v>
+        <v>46274</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46295</v>
+        <v>44917</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6164,8 +6159,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6218,14 +6218,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46294</v>
+        <v>45709</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>6.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46195</v>
+        <v>45916</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45216</v>
+        <v>45258</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45266</v>
+        <v>45184</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45092</v>
+        <v>45936</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45069</v>
+        <v>45219</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6656,14 +6656,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45707</v>
+        <v>46294</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45092</v>
+        <v>45309</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45258</v>
+        <v>45525</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>8.4</v>
+        <v>0.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44983</v>
+        <v>46195</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44670</v>
+        <v>45782</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45520</v>
+        <v>45741</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45782</v>
+        <v>46295</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45741</v>
+        <v>45296</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 41062-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45296</v>
+        <v>46297</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,24 +7303,24 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S 2341-2023</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45106</v>
+        <v>45370</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S 173-2025</t>
+          <t>S 2341-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45677</v>
+        <v>45106</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>25.3</v>
+        <v>21</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S 92-2024</t>
+          <t>S 173-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45301</v>
+        <v>45677</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>11.9</v>
+        <v>25.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7522,148 +7522,221 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
+          <t>S 92-2024</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>S 1331-2025</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D92" s="1" t="n">
+      <c r="D93" s="1" t="n">
         <v>45770</v>
       </c>
-      <c r="E92" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
+      <c r="E93" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
         <v>3.5</v>
       </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>S 2061-2025</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D93" s="1" t="n">
+      <c r="D94" s="1" t="n">
         <v>45839</v>
       </c>
-      <c r="E93" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
+      <c r="E94" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" s="2" t="inlineStr"/>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE94"/>
+  <dimension ref="A1:AE96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45103</v>
+        <v>46183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>12.6</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1186,462 +1186,462 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 5339-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45331</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Kösa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 9316-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45358</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 28478-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45103</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Dvärgpipistrell</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 48309-2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45590</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>1.5</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 26455-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 5339-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45331</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Kösa</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 9316-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45358</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45069</v>
+        <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45216</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44641</v>
+        <v>45197</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45448</v>
+        <v>45275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45365</v>
+        <v>45416</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45883</v>
+        <v>44970</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45812</v>
+        <v>45738</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45939</v>
+        <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>16.1</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45416</v>
+        <v>45939</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>16.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45838</v>
+        <v>45812</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45901</v>
+        <v>45216</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.9</v>
+        <v>8.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44669</v>
+        <v>45448</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44642</v>
+        <v>45901</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>45838</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45738</v>
+        <v>45053</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44670</v>
+        <v>45184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45275</v>
+        <v>46083</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45092</v>
+        <v>45216</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45099</v>
+        <v>45838</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45266</v>
+        <v>45673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45957</v>
+        <v>45673</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46083</v>
+        <v>45957</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45197</v>
+        <v>45883</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45772</v>
+        <v>45525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45772</v>
+        <v>44641</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45772</v>
+        <v>45331</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45520</v>
+        <v>45197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>11.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45548</v>
+        <v>44768</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45092</v>
+        <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44970</v>
+        <v>45365</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45216</v>
+        <v>45772</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.1</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45433</v>
+        <v>45772</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45883</v>
+        <v>45772</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4468,7 +4468,7 @@
         <v>45741</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44571</v>
+        <v>45842</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45520</v>
+        <v>45673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44983</v>
+        <v>45673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45842</v>
+        <v>46184</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45673</v>
+        <v>46188</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4899,14 +4899,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45673</v>
+        <v>45709</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>6.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4976,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45190</v>
+        <v>44917</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4991,8 +4991,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45197</v>
+        <v>44669</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>11.6</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5118,14 +5123,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45707</v>
+        <v>45309</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44768</v>
+        <v>45356</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46184</v>
+        <v>44945</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46188</v>
+        <v>45219</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44518</v>
+        <v>45548</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45216</v>
+        <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45673</v>
+        <v>45520</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45673</v>
+        <v>46274</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45331</v>
+        <v>45916</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5722,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5765,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44623</v>
+        <v>45936</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45356</v>
+        <v>44571</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5868,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44945</v>
+        <v>46295</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45053</v>
+        <v>46294</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6071,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46274</v>
+        <v>46195</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6087,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6130,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44917</v>
+        <v>44642</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6159,13 +6164,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6218,14 +6218,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45709</v>
+        <v>45099</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.7</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 41062-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45916</v>
+        <v>46297</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 41349-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45258</v>
+        <v>46300</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 41352-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45184</v>
+        <v>46300</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45936</v>
+        <v>45216</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45219</v>
+        <v>45266</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46294</v>
+        <v>45092</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45309</v>
+        <v>45069</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6802,14 +6802,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45525</v>
+        <v>45707</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46195</v>
+        <v>45092</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45782</v>
+        <v>45258</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45741</v>
+        <v>44983</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46295</v>
+        <v>44670</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45296</v>
+        <v>45520</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41062-2026</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46297</v>
+        <v>45782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45370</v>
+        <v>45741</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,24 +7376,24 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S 2341-2023</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45106</v>
+        <v>45296</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>21</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,24 +7449,24 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S 173-2025</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45677</v>
+        <v>45370</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>25.3</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7522,7 +7522,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 92-2024</t>
+          <t>S 2341-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45301</v>
+        <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>11.9</v>
+        <v>21</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7595,148 +7595,294 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
+          <t>S 173-2025</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>45677</v>
+      </c>
+      <c r="E93" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>S 92-2024</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E94" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>S 1331-2025</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D93" s="1" t="n">
+      <c r="D95" s="1" t="n">
         <v>45770</v>
       </c>
-      <c r="E93" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
+      <c r="E95" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
         <v>3.5</v>
       </c>
-      <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>S 2061-2025</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D94" s="1" t="n">
+      <c r="D96" s="1" t="n">
         <v>45839</v>
       </c>
-      <c r="E94" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
+      <c r="E96" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" t="n">
-        <v>0</v>
-      </c>
-      <c r="V94" s="2" t="inlineStr"/>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 10274-2022</t>
+          <t>A 21769-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44622</v>
+        <v>45065</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,153 +869,153 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 21769-2023 artfynd.xlsx", "A 21769-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 21769-2023 karta.png", "A 21769-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 21769-2023 georefererad karta.tif", "A 21769-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 21769-2023 FSC-klagomål.docx", "A 21769-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 21769-2023 FSC-klagomål mail.docx", "A 21769-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 21769-2023 tillsynsbegäran.docx", "A 21769-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 21769-2023 tillsynsbegäran mail.docx", "A 21769-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 10274-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44622</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Större vattensalamander
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 10274-2022 artfynd.xlsx", "A 10274-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 10274-2022 karta.png", "A 10274-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 10274-2022 georefererad karta.tif", "A 10274-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 10274-2022 FSC-klagomål.docx", "A 10274-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 10274-2022 FSC-klagomål mail.docx", "A 10274-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 10274-2022 tillsynsbegäran.docx", "A 10274-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 10274-2022 tillsynsbegäran mail.docx", "A 10274-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 21769-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45065</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sankt pers nycklar</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 21769-2023 artfynd.xlsx", "A 21769-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 21769-2023 karta.png", "A 21769-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 21769-2023 georefererad karta.tif", "A 21769-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 21769-2023 FSC-klagomål.docx", "A 21769-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 21769-2023 FSC-klagomål mail.docx", "A 21769-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 21769-2023 tillsynsbegäran.docx", "A 21769-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 21769-2023 tillsynsbegäran mail.docx", "A 21769-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45951</v>
+        <v>45103</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1081,567 +1081,567 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 51772-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Kragjordstjärna</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 48309-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45590</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 26455-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>46183</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>12.6</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Myskmadra</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 5339-2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45331</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>1.9</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Kösa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 9316-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45358</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Gröngöling</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 28478-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45103</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 48309-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45590</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 9520-2022</t>
+          <t>A 12683-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44616</v>
+        <v>44641</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12683-2022</t>
+          <t>A 9520-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44641</v>
+        <v>44616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45433</v>
+        <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>45525</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2205,7 +2205,7 @@
         <v>45197</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45275</v>
+        <v>45782</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45416</v>
+        <v>45741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44970</v>
+        <v>45296</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45738</v>
+        <v>45520</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45190</v>
+        <v>45883</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45939</v>
+        <v>45548</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>16.1</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45812</v>
+        <v>45092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2789,7 +2789,7 @@
         <v>45216</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>8.1</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45448</v>
+        <v>44970</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45901</v>
+        <v>45216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.9</v>
+        <v>8.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45838</v>
+        <v>45433</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45053</v>
+        <v>45370</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45184</v>
+        <v>45901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46083</v>
+        <v>44571</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45216</v>
+        <v>45838</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45838</v>
+        <v>45520</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45673</v>
+        <v>45812</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45673</v>
+        <v>44983</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45957</v>
+        <v>44641</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45883</v>
+        <v>45838</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45525</v>
+        <v>45448</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44641</v>
+        <v>45365</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45331</v>
+        <v>45416</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45197</v>
+        <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>11.6</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44768</v>
+        <v>45673</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45883</v>
+        <v>45673</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45365</v>
+        <v>45190</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45772</v>
+        <v>45197</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>11.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45772</v>
+        <v>44669</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45772</v>
+        <v>44642</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4461,14 +4461,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45741</v>
+        <v>45738</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45842</v>
+        <v>44670</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45673</v>
+        <v>45275</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4680,14 +4680,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45673</v>
+        <v>45707</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46184</v>
+        <v>45772</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46188</v>
+        <v>45772</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4899,14 +4899,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45709</v>
+        <v>45772</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4976,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44917</v>
+        <v>45092</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4991,13 +4991,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44669</v>
+        <v>45099</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5113,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5127,10 +5122,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45309</v>
+        <v>45842</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5143,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5186,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45356</v>
+        <v>44768</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5216,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44945</v>
+        <v>45266</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5289,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45219</v>
+        <v>45741</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45548</v>
+        <v>44518</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44518</v>
+        <v>45216</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45520</v>
+        <v>45939</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5581,7 +5576,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>16.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46274</v>
+        <v>45673</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5654,7 +5649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5711,10 +5706,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45916</v>
+        <v>45673</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45936</v>
+        <v>46184</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44571</v>
+        <v>46188</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46295</v>
+        <v>46083</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46294</v>
+        <v>45331</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46195</v>
+        <v>44623</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44642</v>
+        <v>45356</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45099</v>
+        <v>44945</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6233,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41062-2026</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6290,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46297</v>
+        <v>45053</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6306,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41349-2026</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6363,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46300</v>
+        <v>44917</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6383,8 +6378,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 41352-2026</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6437,14 +6437,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46300</v>
+        <v>45709</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45216</v>
+        <v>45258</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45266</v>
+        <v>45883</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45092</v>
+        <v>45184</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45069</v>
+        <v>45219</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6802,14 +6802,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45707</v>
+        <v>45309</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45092</v>
+        <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45258</v>
+        <v>45916</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44983</v>
+        <v>45936</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44670</v>
+        <v>46294</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45520</v>
+        <v>46195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45782</v>
+        <v>46295</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 41062-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45741</v>
+        <v>46297</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 41349-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45296</v>
+        <v>46300</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 41352-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45370</v>
+        <v>46300</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 21769-2023</t>
+          <t>A 10274-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45065</v>
+        <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -869,153 +869,153 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 10274-2022 artfynd.xlsx", "A 10274-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 10274-2022 karta.png", "A 10274-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 10274-2022 georefererad karta.tif", "A 10274-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 10274-2022 FSC-klagomål.docx", "A 10274-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 10274-2022 FSC-klagomål mail.docx", "A 10274-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 10274-2022 tillsynsbegäran.docx", "A 10274-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 10274-2022 tillsynsbegäran mail.docx", "A 10274-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 21769-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45065</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 21769-2023 artfynd.xlsx", "A 21769-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 21769-2023 karta.png", "A 21769-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 21769-2023 georefererad karta.tif", "A 21769-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 21769-2023 FSC-klagomål.docx", "A 21769-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 21769-2023 FSC-klagomål mail.docx", "A 21769-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 21769-2023 tillsynsbegäran.docx", "A 21769-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 21769-2023 tillsynsbegäran mail.docx", "A 21769-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 10274-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44622</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 10274-2022 artfynd.xlsx", "A 10274-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 10274-2022 karta.png", "A 10274-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 10274-2022 georefererad karta.tif", "A 10274-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 10274-2022 FSC-klagomål.docx", "A 10274-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 10274-2022 FSC-klagomål mail.docx", "A 10274-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 10274-2022 tillsynsbegäran.docx", "A 10274-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 10274-2022 tillsynsbegäran mail.docx", "A 10274-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 51772-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45103</v>
+        <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1081,46 +1081,46 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45951</v>
+        <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,17 +1150,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1190,42 +1190,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45590</v>
+        <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1295,35 +1295,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45331</v>
+        <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,16 +1465,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45358</v>
+        <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 12683-2022</t>
+          <t>A 9520-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44641</v>
+        <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 9520-2022</t>
+          <t>A 12683-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44616</v>
+        <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45069</v>
+        <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45525</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2205,7 +2205,7 @@
         <v>45197</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45782</v>
+        <v>45275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45741</v>
+        <v>45416</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2417,14 +2417,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45296</v>
+        <v>45738</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45520</v>
+        <v>45190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45883</v>
+        <v>44970</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45548</v>
+        <v>45216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>8.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45092</v>
+        <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45216</v>
+        <v>45838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44970</v>
+        <v>45053</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45216</v>
+        <v>45184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.1</v>
+        <v>4.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45433</v>
+        <v>45216</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45370</v>
+        <v>45901</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45901</v>
+        <v>45883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44571</v>
+        <v>45673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45838</v>
+        <v>45673</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45520</v>
+        <v>45838</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45812</v>
+        <v>45525</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44983</v>
+        <v>44641</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44641</v>
+        <v>45331</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45838</v>
+        <v>45197</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>11.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45448</v>
+        <v>44768</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>45365</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45416</v>
+        <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45957</v>
+        <v>45673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45673</v>
+        <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45673</v>
+        <v>45709</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>6.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45190</v>
+        <v>44917</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4188,8 +4188,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4237,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4251,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45197</v>
+        <v>45772</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4267,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>11.6</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4324,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44669</v>
+        <v>45772</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4340,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44642</v>
+        <v>45772</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4456,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4461,14 +4466,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45738</v>
+        <v>44669</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4486,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4529,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4543,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44670</v>
+        <v>45309</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4559,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4602,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4616,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45275</v>
+        <v>45883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4632,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4675,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4680,14 +4685,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45707</v>
+        <v>45356</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4705,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4748,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4762,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45772</v>
+        <v>45741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4778,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45772</v>
+        <v>44945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4851,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45772</v>
+        <v>45939</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45092</v>
+        <v>45219</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45099</v>
+        <v>45548</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45842</v>
+        <v>46083</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44768</v>
+        <v>44518</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45266</v>
+        <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.2</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45741</v>
+        <v>45842</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44518</v>
+        <v>44571</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45216</v>
+        <v>46184</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45939</v>
+        <v>46188</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>16.1</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45673</v>
+        <v>44642</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45673</v>
+        <v>45099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5765,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46184</v>
+        <v>45216</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46188</v>
+        <v>45266</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5868,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>6.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46083</v>
+        <v>45092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45331</v>
+        <v>45069</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6067,14 +6072,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44623</v>
+        <v>45707</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6087,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6130,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45356</v>
+        <v>45092</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6160,7 +6165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6203,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6217,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44945</v>
+        <v>45258</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6233,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6276,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6290,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45053</v>
+        <v>44983</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6306,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6349,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6363,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44917</v>
+        <v>44670</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6378,13 +6383,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6437,14 +6437,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45709</v>
+        <v>45520</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45258</v>
+        <v>45782</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45883</v>
+        <v>45741</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45184</v>
+        <v>45296</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45219</v>
+        <v>45916</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45309</v>
+        <v>45370</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46274</v>
+        <v>45936</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45916</v>
+        <v>45812</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45936</v>
+        <v>46295</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7101,7 +7101,7 @@
         <v>46294</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>46195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 41062-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41062-2026</t>
+          <t>A 41349-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41349-2026</t>
+          <t>A 41352-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7393,7 +7393,7 @@
         <v>46300</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41352-2026</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46300</v>
+        <v>46274</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45951</v>
+        <v>45103</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1081,567 +1081,567 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 48309-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45590</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 51772-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Kragjordstjärna</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 5339-2024</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>45331</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>1.9</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Kösa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 9316-2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45358</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>4</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gröngöling</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 26455-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46183</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>12.6</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Myskmadra</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 28478-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45103</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 48309-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45590</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 9520-2022</t>
+          <t>A 12683-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44616</v>
+        <v>44641</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12683-2022</t>
+          <t>A 9520-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44641</v>
+        <v>44616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45433</v>
+        <v>45548</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>45092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45197</v>
+        <v>44970</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2271,14 +2271,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45275</v>
+        <v>45709</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>6.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45416</v>
+        <v>45216</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2417,14 +2417,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45738</v>
+        <v>45433</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45190</v>
+        <v>45216</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44970</v>
+        <v>45069</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45216</v>
+        <v>45258</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45448</v>
+        <v>45184</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45838</v>
+        <v>44571</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45053</v>
+        <v>45219</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45184</v>
+        <v>45883</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45216</v>
+        <v>45520</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45901</v>
+        <v>45309</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45883</v>
+        <v>45901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45673</v>
+        <v>45525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45673</v>
+        <v>44641</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45838</v>
+        <v>45448</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.3</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45525</v>
+        <v>44983</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44641</v>
+        <v>45782</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45331</v>
+        <v>45838</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45197</v>
+        <v>45741</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>11.6</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44768</v>
+        <v>45365</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45365</v>
+        <v>45296</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45673</v>
+        <v>45416</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3957,7 +3957,7 @@
         <v>45673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45957</v>
+        <v>45673</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45709</v>
+        <v>45370</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.7</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44917</v>
+        <v>44669</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4188,13 +4188,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4237,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4251,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45772</v>
+        <v>44642</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4267,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4310,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4324,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45772</v>
+        <v>45190</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4340,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4383,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45772</v>
+        <v>45197</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4413,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>11.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4456,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4466,14 +4461,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44669</v>
+        <v>45738</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4486,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4529,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4543,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45309</v>
+        <v>44670</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4559,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4602,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4616,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45883</v>
+        <v>45812</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4632,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4675,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4689,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45356</v>
+        <v>45275</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4705,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4748,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4762,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45741</v>
+        <v>45092</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4778,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4821,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44945</v>
+        <v>45099</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4851,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4904,14 +4899,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45939</v>
+        <v>45707</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>16.1</v>
+        <v>0.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45219</v>
+        <v>45957</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45548</v>
+        <v>44768</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5113,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5127,10 +5122,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46083</v>
+        <v>45838</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5143,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5186,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44518</v>
+        <v>45266</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5216,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45520</v>
+        <v>44518</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5289,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45842</v>
+        <v>45216</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44571</v>
+        <v>45197</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46184</v>
+        <v>45673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46188</v>
+        <v>45673</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5581,7 +5576,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44642</v>
+        <v>45520</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5654,7 +5649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5711,10 +5706,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45099</v>
+        <v>45772</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45216</v>
+        <v>45772</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45266</v>
+        <v>45772</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45092</v>
+        <v>45331</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45069</v>
+        <v>45883</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6072,14 +6067,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45707</v>
+        <v>44623</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45092</v>
+        <v>45356</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45258</v>
+        <v>45741</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6233,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8.4</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6290,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44983</v>
+        <v>44945</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6306,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6363,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44670</v>
+        <v>45053</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6379,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6422,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6436,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45520</v>
+        <v>44917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6456,8 +6451,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45782</v>
+        <v>45939</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.5</v>
+        <v>16.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45741</v>
+        <v>46083</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45296</v>
+        <v>45842</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45916</v>
+        <v>46184</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45370</v>
+        <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45936</v>
+        <v>45916</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45812</v>
+        <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46294</v>
+        <v>46195</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46195</v>
+        <v>46295</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41062-2026</t>
+          <t>A 41349-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41349-2026</t>
+          <t>A 41352-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7320,7 +7320,7 @@
         <v>46300</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41352-2026</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46300</v>
+        <v>46274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 41062-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46274</v>
+        <v>46297</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45103</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>45590</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45951</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45331</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44641</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45548</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44970</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45709</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45216</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45433</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45216</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45069</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45258</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45184</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44571</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45219</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45883</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45520</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45309</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>44641</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45448</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>44983</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45782</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45838</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45741</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45365</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45296</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45416</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45673</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45370</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>44669</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>44642</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45190</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45197</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45738</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>44670</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>45812</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>45275</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45092</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45099</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45707</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45957</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44768</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45838</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45266</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44518</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45216</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45197</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>45673</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45520</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45772</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45772</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45772</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>45331</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45883</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44623</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45356</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>45741</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44945</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45053</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45939</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>46083</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45842</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>46184</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45916</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>46294</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>46195</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>46295</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>46300</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>46300</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>46274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>46297</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45103</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>45590</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45951</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45331</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44641</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45548</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44970</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45709</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45216</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45433</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45216</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45069</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45258</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45184</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44571</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45219</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45883</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45520</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45309</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>44641</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45448</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>44983</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45782</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45838</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45741</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45365</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45296</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45416</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45673</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45370</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>44669</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>44642</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45190</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45197</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45738</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>44670</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>45812</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>45275</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45092</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45099</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45707</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45957</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44768</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45838</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45266</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44518</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45216</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45197</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>45673</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45520</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45772</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45772</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45772</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>45331</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45883</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44623</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45356</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>45741</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44945</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45053</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45939</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>46083</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45842</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>46184</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45916</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>46294</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>46195</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>46295</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>46300</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>46300</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>46274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>46297</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45103</v>
+        <v>45590</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1081,46 +1081,46 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45590</v>
+        <v>46183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>12.6</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1190,35 +1190,35 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>45951</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45331</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 26455-2026</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46183</v>
+        <v>45103</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>12.6</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1606,39 +1606,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 12683-2022</t>
+          <t>A 9520-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44641</v>
+        <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 9520-2022</t>
+          <t>A 12683-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44616</v>
+        <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45548</v>
+        <v>45092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45092</v>
+        <v>45069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2198,14 +2198,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44970</v>
+        <v>45707</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2271,14 +2271,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45709</v>
+        <v>45433</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45216</v>
+        <v>45901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>8.1</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45433</v>
+        <v>45092</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45216</v>
+        <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45069</v>
+        <v>46184</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45258</v>
+        <v>46188</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>8.4</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45184</v>
+        <v>45258</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44571</v>
+        <v>44983</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45219</v>
+        <v>44670</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45883</v>
+        <v>45520</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45520</v>
+        <v>45957</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45309</v>
+        <v>45782</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45901</v>
+        <v>45741</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45525</v>
+        <v>45296</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44641</v>
+        <v>45370</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45448</v>
+        <v>45772</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44983</v>
+        <v>45772</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45782</v>
+        <v>45772</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45838</v>
+        <v>45812</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3665,7 +3665,7 @@
         <v>45741</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45365</v>
+        <v>45838</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45296</v>
+        <v>44623</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45416</v>
+        <v>45916</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45673</v>
+        <v>45939</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>16.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45673</v>
+        <v>45936</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45370</v>
+        <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44669</v>
+        <v>46295</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44642</v>
+        <v>46294</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45190</v>
+        <v>46083</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45197</v>
+        <v>46195</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>11.6</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4461,14 +4461,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45738</v>
+        <v>45197</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44670</v>
+        <v>46274</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45812</v>
+        <v>45275</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 41062-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45275</v>
+        <v>46297</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 41349-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45092</v>
+        <v>46300</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 41352-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45099</v>
+        <v>46300</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4899,14 +4899,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45707</v>
+        <v>45883</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4976,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45957</v>
+        <v>45416</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44768</v>
+        <v>44970</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5118,14 +5118,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45838</v>
+        <v>45738</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45266</v>
+        <v>45190</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44518</v>
+        <v>45216</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>8.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45216</v>
+        <v>45448</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45197</v>
+        <v>45053</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45673</v>
+        <v>45184</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45673</v>
+        <v>45216</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45520</v>
+        <v>45842</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45772</v>
+        <v>45673</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45772</v>
+        <v>45673</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45772</v>
+        <v>45525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45331</v>
+        <v>44641</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45883</v>
+        <v>45331</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44623</v>
+        <v>45197</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>11.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6130,7 +6130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45356</v>
+        <v>44768</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6203,7 +6203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45741</v>
+        <v>45365</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6276,7 +6276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44945</v>
+        <v>45673</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6349,7 +6349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45053</v>
+        <v>45673</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6432,14 +6432,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44917</v>
+        <v>45709</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6451,13 +6451,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>6.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6495,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6509,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45939</v>
+        <v>44917</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6529,8 +6524,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>16.1</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46083</v>
+        <v>44669</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45842</v>
+        <v>45309</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46184</v>
+        <v>45356</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46188</v>
+        <v>44945</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45916</v>
+        <v>45219</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45936</v>
+        <v>45548</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46294</v>
+        <v>44518</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46195</v>
+        <v>45520</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46295</v>
+        <v>44571</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41349-2026</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46300</v>
+        <v>44642</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41352-2026</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46300</v>
+        <v>45099</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46274</v>
+        <v>45216</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41062-2026</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46297</v>
+        <v>45266</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 51772-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45590</v>
+        <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1085,563 +1085,563 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 28478-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45103</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 48309-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45590</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 26455-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>46183</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>12.6</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Myskmadra</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 51772-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45951</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 5339-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45331</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Kragjordstjärna</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 5339-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45331</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Kösa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 9316-2024</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45358</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Gröngöling</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 28478-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45103</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45092</v>
+        <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45069</v>
+        <v>45216</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2198,14 +2198,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45707</v>
+        <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45433</v>
+        <v>45883</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45901</v>
+        <v>45370</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45092</v>
+        <v>45901</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45838</v>
+        <v>45812</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46184</v>
+        <v>44641</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46188</v>
+        <v>45838</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45258</v>
+        <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44983</v>
+        <v>45365</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44670</v>
+        <v>45838</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45520</v>
+        <v>45416</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45957</v>
+        <v>45939</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>16.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45782</v>
+        <v>44669</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45741</v>
+        <v>45957</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45296</v>
+        <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45370</v>
+        <v>45738</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45772</v>
+        <v>44670</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45772</v>
+        <v>45275</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45772</v>
+        <v>45092</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45812</v>
+        <v>45099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45741</v>
+        <v>45772</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45838</v>
+        <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44623</v>
+        <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45916</v>
+        <v>45266</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45939</v>
+        <v>46083</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>16.1</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45936</v>
+        <v>45197</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45883</v>
+        <v>45520</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46295</v>
+        <v>45548</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46294</v>
+        <v>45092</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46083</v>
+        <v>44970</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46195</v>
+        <v>45216</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45197</v>
+        <v>45433</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46274</v>
+        <v>45883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45275</v>
+        <v>44571</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41062-2026</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46297</v>
+        <v>45520</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 41349-2026</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46300</v>
+        <v>44983</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 41352-2026</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46300</v>
+        <v>45673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45883</v>
+        <v>45673</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4976,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45416</v>
+        <v>45842</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44970</v>
+        <v>45190</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5118,14 +5118,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45738</v>
+        <v>45197</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>11.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5191,14 +5191,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45190</v>
+        <v>45707</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45216</v>
+        <v>44768</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45448</v>
+        <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45053</v>
+        <v>46188</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45184</v>
+        <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5563,7 +5563,7 @@
         <v>45216</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45842</v>
+        <v>45673</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5709,7 +5709,7 @@
         <v>45673</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45673</v>
+        <v>45331</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45525</v>
+        <v>44623</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44641</v>
+        <v>45356</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45331</v>
+        <v>44945</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45197</v>
+        <v>45053</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>11.6</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6130,7 +6130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44768</v>
+        <v>44917</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6159,8 +6159,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6203,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6213,14 +6218,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45365</v>
+        <v>45709</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6233,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6276,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6290,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45673</v>
+        <v>45258</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6306,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>8.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6349,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6363,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45673</v>
+        <v>45916</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6379,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6422,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6432,14 +6437,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45709</v>
+        <v>45184</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6452,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6495,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6509,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44917</v>
+        <v>45936</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6524,13 +6529,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44669</v>
+        <v>45219</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45309</v>
+        <v>46294</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45356</v>
+        <v>45309</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44945</v>
+        <v>45525</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45219</v>
+        <v>46195</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45548</v>
+        <v>45782</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44518</v>
+        <v>46295</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45520</v>
+        <v>45741</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44571</v>
+        <v>45296</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 41349-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44642</v>
+        <v>46300</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 41352-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45099</v>
+        <v>46300</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45216</v>
+        <v>46274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 41062-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45266</v>
+        <v>46297</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45103</v>
+        <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,17 +1150,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1186,46 +1186,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45590</v>
+        <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1295,35 +1295,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45331</v>
+        <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,16 +1465,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45358</v>
+        <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12683-2022</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44641</v>
+        <v>45370</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 12683-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45069</v>
+        <v>44641</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45216</v>
+        <v>45433</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45741</v>
+        <v>45812</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45883</v>
+        <v>45838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2344,14 +2344,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45370</v>
+        <v>45709</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>6.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>45901</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45812</v>
+        <v>44623</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44641</v>
+        <v>45838</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45838</v>
+        <v>45883</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45448</v>
+        <v>44917</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2728,8 +2728,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2777,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2791,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45365</v>
+        <v>45197</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2807,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2850,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2864,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45838</v>
+        <v>45275</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2880,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2935,7 +2940,7 @@
         <v>45416</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2991,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45939</v>
+        <v>44970</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>16.1</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44669</v>
+        <v>46083</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3147,14 +3152,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45957</v>
+        <v>45738</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3172,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3229,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44642</v>
+        <v>45190</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3283,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3293,14 +3298,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45738</v>
+        <v>45957</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44670</v>
+        <v>44669</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3391,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3434,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3448,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45275</v>
+        <v>45216</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3464,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3507,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3521,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45092</v>
+        <v>45448</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3537,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3580,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3594,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45099</v>
+        <v>45309</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3610,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3653,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3667,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45772</v>
+        <v>45053</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3683,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3726,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3740,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45772</v>
+        <v>45184</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3756,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3799,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3813,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45772</v>
+        <v>45356</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3829,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3872,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3886,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45266</v>
+        <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3902,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3945,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3959,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46083</v>
+        <v>45772</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3975,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4018,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4032,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45197</v>
+        <v>45772</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4048,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4091,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4105,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45520</v>
+        <v>45216</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4121,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4164,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4178,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45548</v>
+        <v>45673</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4194,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4237,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4251,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45092</v>
+        <v>45673</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4267,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4324,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44970</v>
+        <v>45883</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4340,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45216</v>
+        <v>45525</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4456,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4470,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45433</v>
+        <v>45741</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4486,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4529,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4543,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45883</v>
+        <v>44641</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4559,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4602,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4616,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44571</v>
+        <v>45331</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4632,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4675,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4689,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45520</v>
+        <v>45197</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4705,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>11.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4748,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4762,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44983</v>
+        <v>44768</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4778,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45673</v>
+        <v>45365</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4851,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45673</v>
+        <v>45939</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>16.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45842</v>
+        <v>45673</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45190</v>
+        <v>45673</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5108,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45197</v>
+        <v>44945</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>11.6</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5191,14 +5196,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45707</v>
+        <v>45842</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44768</v>
+        <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46184</v>
+        <v>45548</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46188</v>
+        <v>44518</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44518</v>
+        <v>45520</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45216</v>
+        <v>46184</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45673</v>
+        <v>46188</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45673</v>
+        <v>44571</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5722,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5765,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45331</v>
+        <v>44642</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44623</v>
+        <v>45916</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5868,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45356</v>
+        <v>45099</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44945</v>
+        <v>45216</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6071,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45053</v>
+        <v>45266</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6087,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6130,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44917</v>
+        <v>45936</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6159,13 +6164,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6218,14 +6218,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45709</v>
+        <v>45092</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45258</v>
+        <v>45069</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6364,14 +6364,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45916</v>
+        <v>45707</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.4</v>
+        <v>0.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45184</v>
+        <v>45092</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45936</v>
+        <v>46295</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45219</v>
+        <v>46294</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46294</v>
+        <v>46195</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45309</v>
+        <v>45258</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45525</v>
+        <v>44983</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46195</v>
+        <v>44670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45782</v>
+        <v>45520</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46295</v>
+        <v>46274</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45741</v>
+        <v>45782</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 41062-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45296</v>
+        <v>46297</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41349-2026</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46300</v>
+        <v>45741</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41352-2026</t>
+          <t>A 41349-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7320,7 +7320,7 @@
         <v>46300</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 41352-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46274</v>
+        <v>46300</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41062-2026</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46297</v>
+        <v>45296</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45951</v>
+        <v>45103</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1081,46 +1081,46 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45331</v>
+        <v>45590</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1190,143 +1190,143 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 5339-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45331</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Kösa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 9316-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45358</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45103</v>
+        <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 51772-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45590</v>
+        <v>45951</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 12683-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45370</v>
+        <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12683-2022</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44641</v>
+        <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45433</v>
+        <v>45069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45812</v>
+        <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45838</v>
+        <v>45812</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2344,14 +2344,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45709</v>
+        <v>45883</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45901</v>
+        <v>45548</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44623</v>
+        <v>45092</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45838</v>
+        <v>44970</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45883</v>
+        <v>45216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44917</v>
+        <v>45838</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2728,13 +2728,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2777,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2791,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45197</v>
+        <v>45216</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2807,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>8.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2850,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2864,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45275</v>
+        <v>45433</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2880,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2923,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45416</v>
+        <v>44571</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2996,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3010,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44970</v>
+        <v>45520</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3026,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3069,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46083</v>
+        <v>44641</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3152,14 +3147,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45738</v>
+        <v>45448</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3172,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3229,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45190</v>
+        <v>45365</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45957</v>
+        <v>44983</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44669</v>
+        <v>45416</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3391,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3434,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3448,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45216</v>
+        <v>45901</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3464,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.1</v>
+        <v>3.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3507,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3521,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45448</v>
+        <v>44669</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3537,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3580,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3594,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45309</v>
+        <v>44642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3610,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3653,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3667,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45053</v>
+        <v>45673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3683,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3726,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45184</v>
+        <v>45673</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3756,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3799,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3809,14 +3804,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45356</v>
+        <v>45738</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3829,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3872,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3886,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45772</v>
+        <v>44670</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3902,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3945,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45772</v>
+        <v>45190</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3975,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4018,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4032,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45772</v>
+        <v>45197</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4048,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>11.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4091,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4105,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45216</v>
+        <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4121,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4164,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4178,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45673</v>
+        <v>45275</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4194,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4237,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4251,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45673</v>
+        <v>45092</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4267,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4310,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4324,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45883</v>
+        <v>45099</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4340,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4383,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4393,14 +4388,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45525</v>
+        <v>45707</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4413,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4456,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4470,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45741</v>
+        <v>45266</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4486,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4529,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4543,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44641</v>
+        <v>44768</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4559,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4602,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4616,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45331</v>
+        <v>45838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4632,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4675,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4689,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45197</v>
+        <v>45842</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4705,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>11.6</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4748,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4762,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44768</v>
+        <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4778,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4821,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45365</v>
+        <v>45216</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4851,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45939</v>
+        <v>45673</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>16.1</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4984,7 +4979,7 @@
         <v>45673</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45673</v>
+        <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5113,7 +5108,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5127,10 +5122,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44945</v>
+        <v>45331</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5143,7 +5138,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5186,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45842</v>
+        <v>46188</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5216,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45219</v>
+        <v>44623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5289,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45548</v>
+        <v>45356</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44518</v>
+        <v>44945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45520</v>
+        <v>45053</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46184</v>
+        <v>44917</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5580,8 +5575,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46188</v>
+        <v>45957</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5707,14 +5707,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44571</v>
+        <v>45709</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44642</v>
+        <v>45258</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44493-2025</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45916</v>
+        <v>45184</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45099</v>
+        <v>45219</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45216</v>
+        <v>45916</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45266</v>
+        <v>45309</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6152,7 +6152,7 @@
         <v>45936</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45092</v>
+        <v>45525</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45069</v>
+        <v>46294</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6364,14 +6364,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45707</v>
+        <v>45782</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.2</v>
+        <v>5.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45092</v>
+        <v>45772</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46295</v>
+        <v>45772</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46294</v>
+        <v>45772</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46195</v>
+        <v>45741</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45258</v>
+        <v>45296</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>8.4</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44983</v>
+        <v>46195</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44670</v>
+        <v>46295</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45520</v>
+        <v>45370</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46274</v>
+        <v>45741</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 41349-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45782</v>
+        <v>46300</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41062-2026</t>
+          <t>A 41352-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45741</v>
+        <v>46274</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41349-2026</t>
+          <t>A 41062-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41352-2026</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46300</v>
+        <v>45939</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>16.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45296</v>
+        <v>46083</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 51772-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45103</v>
+        <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1081,46 +1081,46 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45590</v>
+        <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,17 +1150,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1190,42 +1190,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45331</v>
+        <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1295,35 +1295,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45358</v>
+        <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 51772-2025</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45951</v>
+        <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 51772-2025 artfynd.xlsx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 51772-2025 karta.png", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 51772-2025 georefererad karta.tif", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 51772-2025 FSC-klagomål.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 51772-2025 FSC-klagomål mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 51772-2025 tillsynsbegäran.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 51772-2025 tillsynsbegäran mail.docx", "A 51772-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45197</v>
+        <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45069</v>
+        <v>45197</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45520</v>
+        <v>45275</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45812</v>
+        <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45883</v>
+        <v>45416</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45548</v>
+        <v>44970</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45092</v>
+        <v>45738</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44970</v>
+        <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2643,7 +2643,7 @@
         <v>45216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>8.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45838</v>
+        <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45216</v>
+        <v>45053</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45433</v>
+        <v>45184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44571</v>
+        <v>45216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45520</v>
+        <v>45883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44641</v>
+        <v>45673</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45448</v>
+        <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45365</v>
+        <v>45525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44983</v>
+        <v>44641</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45416</v>
+        <v>45901</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45901</v>
+        <v>45331</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44669</v>
+        <v>45197</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.7</v>
+        <v>11.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44642</v>
+        <v>44768</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45673</v>
+        <v>45365</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45673</v>
+        <v>45838</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>6.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3804,14 +3804,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45738</v>
+        <v>45673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44670</v>
+        <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45190</v>
+        <v>45842</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45197</v>
+        <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>11.6</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45883</v>
+        <v>45709</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45275</v>
+        <v>44917</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4188,8 +4188,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4237,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4251,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45092</v>
+        <v>44669</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4267,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4324,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45099</v>
+        <v>45309</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4340,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4388,14 +4393,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45707</v>
+        <v>45772</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4456,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,10 +4470,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45266</v>
+        <v>45356</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4486,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4529,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4543,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44768</v>
+        <v>45772</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4559,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4602,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4616,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45838</v>
+        <v>45772</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4632,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4675,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4689,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45842</v>
+        <v>44945</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4705,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4748,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4762,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44518</v>
+        <v>45741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4778,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45216</v>
+        <v>45219</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4846,7 +4851,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45673</v>
+        <v>45939</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>16.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45673</v>
+        <v>45548</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5052,7 +5057,7 @@
         <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5108,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45331</v>
+        <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5198,7 +5203,7 @@
         <v>46188</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44623</v>
+        <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45356</v>
+        <v>46083</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44945</v>
+        <v>44571</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45053</v>
+        <v>44642</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44917</v>
+        <v>45099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5575,13 +5580,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45957</v>
+        <v>45216</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5707,14 +5707,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45709</v>
+        <v>45266</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45258</v>
+        <v>45092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45184</v>
+        <v>45069</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5926,14 +5926,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45219</v>
+        <v>45707</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6006,7 +6006,7 @@
         <v>45916</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45309</v>
+        <v>45092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6152,7 +6152,7 @@
         <v>45936</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45525</v>
+        <v>46295</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46294</v>
+        <v>45258</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45782</v>
+        <v>46294</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45772</v>
+        <v>44983</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45772</v>
+        <v>44670</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45772</v>
+        <v>46195</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45741</v>
+        <v>45520</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45296</v>
+        <v>45782</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46195</v>
+        <v>45741</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46295</v>
+        <v>45296</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45370</v>
+        <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45741</v>
+        <v>45370</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41349-2026</t>
+          <t>A 41062-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41352-2026</t>
+          <t>A 41349-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7174,7 +7174,7 @@
         <v>46300</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 41352-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46274</v>
+        <v>46300</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41062-2026</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46297</v>
+        <v>45812</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45939</v>
+        <v>45838</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>16.1</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46083</v>
+        <v>45883</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45197</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45275</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45416</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44970</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45738</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45053</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45673</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>44641</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45901</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45331</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45197</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>44768</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45365</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45838</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45842</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45709</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>44917</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44669</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45309</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45772</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45356</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>45772</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>45772</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44945</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45219</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45939</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45548</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46188</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46083</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>44571</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>44642</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45216</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45266</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45069</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45707</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45916</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>45092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45936</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>46295</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>45258</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>46294</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44983</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44670</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>46195</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45520</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45782</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>45741</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45296</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45370</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>46297</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>46300</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>46300</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45812</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45838</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45883</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45103</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45590</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44488</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44641</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45433</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45197</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45275</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45416</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44970</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45738</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45448</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45053</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45673</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>44641</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45901</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45331</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45197</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>44768</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45365</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45838</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45842</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45709</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>44917</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44669</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45309</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45772</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45356</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>45772</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>45772</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44945</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45219</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45939</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45548</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46188</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46083</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>44571</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>44642</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45216</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45266</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45069</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45707</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45916</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>45092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45936</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>46295</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>45258</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>46294</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44983</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44670</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>46195</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45520</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45782</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>45741</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45296</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45370</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>46297</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>46300</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>46300</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45812</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45838</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45883</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45770</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE96"/>
+  <dimension ref="A1:AE95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5339-2024</t>
+          <t>A 28478-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45331</v>
+        <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1186,46 +1186,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 9316-2024</t>
+          <t>A 48309-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45358</v>
+        <v>45590</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1295,35 +1295,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         <v>46183</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 5339-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45103</v>
+        <v>45331</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,46 +1501,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 48309-2024</t>
+          <t>A 9316-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45590</v>
+        <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58607-2021</t>
+          <t>A 9520-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1833,14 +1833,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44488</v>
+        <v>44616</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 9520-2022</t>
+          <t>A 12683-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44616</v>
+        <v>44641</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12683-2022</t>
+          <t>A 22561-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44641</v>
+        <v>45069</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45433</v>
+        <v>45216</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45197</v>
+        <v>44641</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45275</v>
+        <v>45448</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44623</v>
+        <v>45365</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
         <v>45416</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44970</v>
+        <v>44669</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45738</v>
+        <v>44642</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 16297-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45190</v>
+        <v>44670</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2636,14 +2636,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45216</v>
+        <v>45738</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 26478-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45448</v>
+        <v>45092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 28080-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45053</v>
+        <v>45099</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44752-2023</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45184</v>
+        <v>45275</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45216</v>
+        <v>45883</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 62334-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45883</v>
+        <v>45266</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45673</v>
+        <v>45901</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45673</v>
+        <v>45838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34394-2024</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45525</v>
+        <v>45197</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44641</v>
+        <v>45520</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45901</v>
+        <v>45548</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 26493-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45331</v>
+        <v>45092</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45197</v>
+        <v>44970</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>11.6</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44768</v>
+        <v>45216</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45365</v>
+        <v>45433</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45838</v>
+        <v>45957</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45673</v>
+        <v>45842</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45673</v>
+        <v>44571</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 33742-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45842</v>
+        <v>45520</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45957</v>
+        <v>45772</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45709</v>
+        <v>45772</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.7</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44917</v>
+        <v>45772</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4188,13 +4188,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4237,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 9602-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4251,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44669</v>
+        <v>44983</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4267,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4310,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2089-2024</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4324,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45309</v>
+        <v>45741</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4340,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4383,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45772</v>
+        <v>45673</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4413,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4456,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4470,10 +4465,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45356</v>
+        <v>45673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4486,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4529,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4543,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45772</v>
+        <v>45190</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4559,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4602,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4616,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45772</v>
+        <v>45197</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4632,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>11.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4675,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4689,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44945</v>
+        <v>45939</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4705,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>16.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4748,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 8130-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4758,14 +4753,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45741</v>
+        <v>45707</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4778,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4821,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51284-2023</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45219</v>
+        <v>46184</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4851,7 +4846,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45939</v>
+        <v>44768</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4919,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>16.1</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4962,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45548</v>
+        <v>46083</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +4992,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5035,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5049,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5065,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5130,7 +5125,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5186,7 +5181,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 52089-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46188</v>
+        <v>45216</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5216,7 +5211,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45520</v>
+        <v>45673</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5289,7 +5284,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46083</v>
+        <v>45673</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44571</v>
+        <v>45883</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44642</v>
+        <v>45331</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5508,7 +5503,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45099</v>
+        <v>44623</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5581,7 +5576,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45216</v>
+        <v>45356</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5654,7 +5649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5697,7 +5692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5711,10 +5706,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45266</v>
+        <v>44945</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5727,7 +5722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5770,7 +5765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45092</v>
+        <v>45053</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5800,7 +5795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5843,7 +5838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5857,10 +5852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45069</v>
+        <v>44917</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5872,8 +5867,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>6.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6006,7 +6006,7 @@
         <v>45916</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 60469-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45092</v>
+        <v>45258</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48751-2025</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45936</v>
+        <v>45184</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40555-2026</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46295</v>
+        <v>45219</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60469-2023</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45258</v>
+        <v>46294</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40321-2026</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46294</v>
+        <v>45309</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 28082-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44983</v>
+        <v>46195</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44670</v>
+        <v>45525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28082-2026</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46195</v>
+        <v>46295</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 21464-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45520</v>
+        <v>45782</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21464-2025</t>
+          <t>A 14475-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45782</v>
+        <v>45741</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14475-2025</t>
+          <t>A 445-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45741</v>
+        <v>45296</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 445-2024</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45296</v>
+        <v>45370</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37232-2026</t>
+          <t>A 41349-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46274</v>
+        <v>46300</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10997-2024</t>
+          <t>A 41352-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45370</v>
+        <v>46300</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41062-2026</t>
+          <t>A 37232-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46297</v>
+        <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41349-2026</t>
+          <t>A 41062-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41352-2026</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46300</v>
+        <v>45812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 27402-2025</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45812</v>
+        <v>45838</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32514-2025</t>
+          <t>A 48751-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45838</v>
+        <v>45936</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7449,24 +7449,24 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>S 2341-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45883</v>
+        <v>45106</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>21</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7522,7 +7522,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 2341-2023</t>
+          <t>S 173-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45106</v>
+        <v>45677</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>21</v>
+        <v>25.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7595,7 +7595,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 173-2025</t>
+          <t>S 92-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45677</v>
+        <v>45301</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>25.3</v>
+        <v>11.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7668,7 +7668,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 92-2024</t>
+          <t>S 1331-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45301</v>
+        <v>45770</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>11.9</v>
+        <v>3.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7738,10 +7738,10 @@
       </c>
       <c r="V94" s="2" t="inlineStr"/>
     </row>
-    <row r="95" ht="15" customHeight="1">
+    <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 1331-2025</t>
+          <t>S 2061-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7751,14 +7751,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45770</v>
+        <v>45839</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7810,79 +7810,6 @@
         <v>0</v>
       </c>
       <c r="V95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>S 2061-2025</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="E96" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SÖLVESBORG.xlsx
+++ b/Översikt SÖLVESBORG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE95"/>
+  <dimension ref="A1:AE101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44622</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45065</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45951</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 28478-2023</t>
+          <t>A 26455-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45103</v>
+        <v>46183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>12.6</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1186,462 +1186,462 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 5339-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45331</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Kösa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 9316-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45358</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 28478-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45103</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Dvärgpipistrell</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 28478-2023 artfynd.xlsx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 28478-2023 karta.png", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 28478-2023 georefererad karta.tif", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 28478-2023 FSC-klagomål.docx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 28478-2023 FSC-klagomål mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 28478-2023 tillsynsbegäran.docx", "A 28478-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 28478-2023 tillsynsbegäran mail.docx", "A 28478-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 48309-2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45590</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SÖLVESBORG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>1.5</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 48309-2024 artfynd.xlsx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 48309-2024 karta.png", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 48309-2024 georefererad karta.tif", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 48309-2024 FSC-klagomål.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 48309-2024 FSC-klagomål mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 48309-2024 tillsynsbegäran.docx", "A 48309-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 48309-2024 tillsynsbegäran mail.docx", "A 48309-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 26455-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 26455-2026 artfynd.xlsx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 26455-2026 karta.png", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 26455-2026 georefererad karta.tif", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 26455-2026 FSC-klagomål.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 26455-2026 FSC-klagomål mail.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 26455-2026 tillsynsbegäran.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 26455-2026 tillsynsbegäran mail.docx", "A 26455-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 5339-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45331</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Kösa</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 5339-2024 artfynd.xlsx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 5339-2024 karta.png", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 5339-2024 georefererad karta.tif", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 5339-2024 FSC-klagomål.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 5339-2024 FSC-klagomål mail.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 5339-2024 tillsynsbegäran.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 5339-2024 tillsynsbegäran mail.docx", "A 5339-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 9316-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45358</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SÖLVESBORG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/artfynd/A 9316-2024 artfynd.xlsx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor/A 9316-2024 karta.png", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/kartor_geotiff/A 9316-2024 georefererad karta.tif", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomål/A 9316-2024 FSC-klagomål.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/klagomålsmail/A 9316-2024 FSC-klagomål mail.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsyn/A 9316-2024 tillsynsbegäran.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1083/tillsynsmail/A 9316-2024 tillsynsbegäran mail.docx", "A 9316-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44616</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44641</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22561-2023</t>
+          <t>A 19827-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45069</v>
+        <v>45433</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52084-2023</t>
+          <t>A 10403-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45216</v>
+        <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12298-2022</t>
+          <t>A 10997-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44641</v>
+        <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22906-2024</t>
+          <t>A 14481-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45448</v>
+        <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10390-2024</t>
+          <t>A 27402-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45365</v>
+        <v>45812</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17612-2024</t>
+          <t>A 41565-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45416</v>
+        <v>45901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16188-2022</t>
+          <t>A 46500-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44669</v>
+        <v>45197</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12848-2022</t>
+          <t>A 32436-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44642</v>
+        <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16297-2022</t>
+          <t>A 49688-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44670</v>
+        <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>16.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14136-2025</t>
+          <t>A 63571-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2636,14 +2636,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45738</v>
+        <v>45275</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 26478-2023</t>
+          <t>A 17612-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45092</v>
+        <v>45416</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28080-2023</t>
+          <t>A 7134-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45099</v>
+        <v>44970</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 63571-2023</t>
+          <t>A 14136-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2855,14 +2855,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45275</v>
+        <v>45738</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38406-2025</t>
+          <t>A 44871-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45883</v>
+        <v>45190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62334-2023</t>
+          <t>A 52086-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45266</v>
+        <v>45216</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41565-2025</t>
+          <t>A 22906-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45901</v>
+        <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32436-2025</t>
+          <t>A 11528-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45838</v>
+        <v>46083</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 46500-2023</t>
+          <t>A 20164-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45197</v>
+        <v>45053</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33766-2024</t>
+          <t>A 44752-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45520</v>
+        <v>45184</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39130-2024</t>
+          <t>A 52893-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45548</v>
+        <v>45957</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26493-2023</t>
+          <t>A 52084-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45092</v>
+        <v>45216</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7134-2023</t>
+          <t>A 32514-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44970</v>
+        <v>45838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52086-2023</t>
+          <t>A 2327-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45216</v>
+        <v>45673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19827-2024</t>
+          <t>A 2325-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45433</v>
+        <v>45673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52893-2025</t>
+          <t>A 20093-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45957</v>
+        <v>45772</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33817-2025</t>
+          <t>A 20155-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45842</v>
+        <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1070-2022</t>
+          <t>A 20127-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44571</v>
+        <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33742-2024</t>
+          <t>A 34394-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45520</v>
+        <v>45525</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20127-2025</t>
+          <t>A 12298-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45772</v>
+        <v>44641</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20093-2025</t>
+          <t>A 38317-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45772</v>
+        <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 20155-2025</t>
+          <t>A 5407-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45772</v>
+        <v>45331</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9602-2023</t>
+          <t>A 47242-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44983</v>
+        <v>45197</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>11.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14481-2025</t>
+          <t>A 30992-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45741</v>
+        <v>44768</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2200-2025</t>
+          <t>A 10390-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45673</v>
+        <v>45365</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2210-2025</t>
+          <t>A 2200-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4468,7 +4468,7 @@
         <v>45673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 44871-2023</t>
+          <t>A 2210-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45190</v>
+        <v>45673</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47242-2023</t>
+          <t>A 38406-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45197</v>
+        <v>45883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>11.6</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49688-2025</t>
+          <t>A 33817-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45939</v>
+        <v>45842</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>16.1</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8130-2025</t>
+          <t>A 8523-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>6.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26744-2026</t>
+          <t>A 61767-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46184</v>
+        <v>44917</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4845,8 +4845,13 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30992-2022</t>
+          <t>A 16188-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44768</v>
+        <v>44669</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11528-2026</t>
+          <t>A 2089-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46083</v>
+        <v>45309</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27151-2026</t>
+          <t>A 8837-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46188</v>
+        <v>45356</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5108,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 66447-2021</t>
+          <t>A 2832-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44518</v>
+        <v>44945</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52089-2023</t>
+          <t>A 26744-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45216</v>
+        <v>46184</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2327-2025</t>
+          <t>A 27151-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45673</v>
+        <v>46188</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2325-2025</t>
+          <t>A 51284-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45673</v>
+        <v>45219</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 38317-2025</t>
+          <t>A 39130-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45883</v>
+        <v>45548</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5407-2024</t>
+          <t>A 66447-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45331</v>
+        <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10403-2022</t>
+          <t>A 33766-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44623</v>
+        <v>45520</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8837-2024</t>
+          <t>A 44493-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45356</v>
+        <v>45916</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2832-2023</t>
+          <t>A 1070-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44945</v>
+        <v>44571</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5722,7 +5727,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5765,7 +5770,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20164-2023</t>
+          <t>A 40555-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45053</v>
+        <v>46295</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 61767-2022</t>
+          <t>A 40321-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44917</v>
+        <v>46294</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5867,13 +5872,8 @@
           <t>SÖLVESBORG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8523-2025</t>
+          <t>A 12848-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5926,14 +5926,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45709</v>
+        <v>44642</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6.7</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5989,7 +5989,7 @@
     <row r="71" ht="15" customHeight="1">
  